--- a/Results/Tables/Predict-AML2.0.xlsx
+++ b/Results/Tables/Predict-AML2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="933">
   <si>
     <t>Method</t>
   </si>
@@ -1132,1227 +1132,1230 @@
     <t>0.311 +/- 0.078</t>
   </si>
   <si>
-    <t>31.453 +/- 0.959</t>
-  </si>
-  <si>
-    <t>43.181 +/- 1.526</t>
-  </si>
-  <si>
-    <t>0.512 +/- 0.019</t>
-  </si>
-  <si>
-    <t>0.716 +/- 0.013</t>
+    <t>31.054 +/- 0.742</t>
+  </si>
+  <si>
+    <t>42.687 +/- 1.458</t>
+  </si>
+  <si>
+    <t>0.525 +/- 0.021</t>
+  </si>
+  <si>
+    <t>0.724 +/- 0.015</t>
+  </si>
+  <si>
+    <t>0.719 +/- 0.011</t>
+  </si>
+  <si>
+    <t>26.009 +/- 0.266</t>
+  </si>
+  <si>
+    <t>36.423 +/- 0.249</t>
+  </si>
+  <si>
+    <t>0.651 +/- 0.003</t>
+  </si>
+  <si>
+    <t>45.285 +/- 3.859</t>
+  </si>
+  <si>
+    <t>57.409 +/- 4.639</t>
+  </si>
+  <si>
+    <t>0.150 +/- 0.065</t>
+  </si>
+  <si>
+    <t>0.377 +/- 0.088</t>
+  </si>
+  <si>
+    <t>0.348 +/- 0.096</t>
+  </si>
+  <si>
+    <t>31.574 +/- 1.417</t>
+  </si>
+  <si>
+    <t>43.230 +/- 1.860</t>
+  </si>
+  <si>
+    <t>0.512 +/- 0.032</t>
+  </si>
+  <si>
+    <t>0.715 +/- 0.022</t>
+  </si>
+  <si>
+    <t>0.709 +/- 0.028</t>
+  </si>
+  <si>
+    <t>25.995 +/- 0.259</t>
+  </si>
+  <si>
+    <t>36.373 +/- 0.219</t>
+  </si>
+  <si>
+    <t>0.652 +/- 0.003</t>
+  </si>
+  <si>
+    <t>0.808 +/- 0.001</t>
+  </si>
+  <si>
+    <t>45.227 +/- 1.978</t>
+  </si>
+  <si>
+    <t>57.499 +/- 3.396</t>
+  </si>
+  <si>
+    <t>0.139 +/- 0.019</t>
+  </si>
+  <si>
+    <t>0.372 +/- 0.024</t>
+  </si>
+  <si>
+    <t>0.346 +/- 0.030</t>
+  </si>
+  <si>
+    <t>31.592 +/- 1.327</t>
+  </si>
+  <si>
+    <t>43.138 +/- 2.793</t>
+  </si>
+  <si>
+    <t>0.513 +/- 0.034</t>
+  </si>
+  <si>
+    <t>0.716 +/- 0.024</t>
+  </si>
+  <si>
+    <t>0.708 +/- 0.019</t>
+  </si>
+  <si>
+    <t>CNN</t>
+  </si>
+  <si>
+    <t>23.039 ± 0.161</t>
+  </si>
+  <si>
+    <t>33.460 ± 0.188</t>
+  </si>
+  <si>
+    <t>0.708 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.841 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.839 ± 0.001</t>
+  </si>
+  <si>
+    <t>49.872 ± 3.180</t>
+  </si>
+  <si>
+    <t>65.263 ± 4.417</t>
+  </si>
+  <si>
+    <t>0.170 ± 0.034</t>
+  </si>
+  <si>
+    <t>0.358 ± 0.065</t>
+  </si>
+  <si>
+    <t>0.366 ± 0.050</t>
+  </si>
+  <si>
+    <t>32.174 ± 0.756</t>
+  </si>
+  <si>
+    <t>42.891 ± 1.195</t>
+  </si>
+  <si>
+    <t>0.500 ± 0.017</t>
+  </si>
+  <si>
+    <t>0.707 ± 0.012</t>
+  </si>
+  <si>
+    <t>0.704 ± 0.011</t>
+  </si>
+  <si>
+    <t>22.883 ± 0.152</t>
+  </si>
+  <si>
+    <t>33.260 ± 0.251</t>
+  </si>
+  <si>
+    <t>0.711 ± 0.005</t>
+  </si>
+  <si>
+    <t>0.843 ± 0.003</t>
+  </si>
+  <si>
+    <t>51.028 ± 2.534</t>
+  </si>
+  <si>
+    <t>65.739 ± 3.695</t>
+  </si>
+  <si>
+    <t>0.003 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.025 ± 0.057</t>
+  </si>
+  <si>
+    <t>0.070 ±0.059</t>
+  </si>
+  <si>
+    <t>34.225 ± 0.582</t>
+  </si>
+  <si>
+    <t>44.239 ± 0.941</t>
+  </si>
+  <si>
+    <t>0.504 ± 0.014</t>
+  </si>
+  <si>
+    <t>0.710 ± 0.010</t>
+  </si>
+  <si>
+    <t>0.701 ± 0.008</t>
+  </si>
+  <si>
+    <t>22.946 ± 0.170</t>
+  </si>
+  <si>
+    <t>33.250 ± 0.206</t>
+  </si>
+  <si>
+    <t>0.711 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.840 ± 0.002</t>
+  </si>
+  <si>
+    <t>49.115 ± 2.833</t>
+  </si>
+  <si>
+    <t>66.549 ± 4.753</t>
+  </si>
+  <si>
+    <t>0.059 ±  0.034</t>
+  </si>
+  <si>
+    <t>0.234 ± 0.070</t>
+  </si>
+  <si>
+    <t>0.259 ± 0.045</t>
+  </si>
+  <si>
+    <t>31.466 ± 0.545</t>
+  </si>
+  <si>
+    <t>41.847 ± 1.145</t>
+  </si>
+  <si>
+    <t>0.528 ± 0.016</t>
+  </si>
+  <si>
+    <t>0.726 ± 0.011</t>
+  </si>
+  <si>
+    <t>0.719 ± 0.008</t>
+  </si>
+  <si>
+    <t>22.758 ± 0.157</t>
+  </si>
+  <si>
+    <t>32.757 ± 0.246</t>
+  </si>
+  <si>
+    <t>0.718 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.848 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.844 ± 0.002</t>
+  </si>
+  <si>
+    <t>49.096 ± 2.723</t>
+  </si>
+  <si>
+    <t>64.816 ± 4.040</t>
+  </si>
+  <si>
+    <t>0.065 ± 0.031</t>
+  </si>
+  <si>
+    <t>0.249 ± 0.063</t>
+  </si>
+  <si>
+    <t>0.244 ± 0.052</t>
+  </si>
+  <si>
+    <t>32.106 ± 0.498</t>
+  </si>
+  <si>
+    <t>43.058 ± 1.107</t>
+  </si>
+  <si>
+    <t>0.506 ± 0.014</t>
+  </si>
+  <si>
+    <t>0.711 ± 0.010</t>
+  </si>
+  <si>
+    <t>0.701 ± 0.007</t>
+  </si>
+  <si>
+    <t>LSTM</t>
+  </si>
+  <si>
+    <t>23.528 ± 0.166</t>
+  </si>
+  <si>
+    <t>33.527 ± 0.229</t>
+  </si>
+  <si>
+    <t>0.705 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.834 ± 0.002</t>
+  </si>
+  <si>
+    <t>46.551 ± 3.168</t>
+  </si>
+  <si>
+    <t>62.456 ± 4.331</t>
+  </si>
+  <si>
+    <t>0.183 ± 0.031</t>
+  </si>
+  <si>
+    <t>0.383 ± 0.054</t>
+  </si>
+  <si>
+    <t>0.419 ± 0.047</t>
+  </si>
+  <si>
+    <t>33.370 ± 0.582</t>
+  </si>
+  <si>
+    <t>44.839 ± 0.853</t>
+  </si>
+  <si>
+    <t>0.460 ± 0.011</t>
+  </si>
+  <si>
+    <t>0.678 ± 0.008</t>
+  </si>
+  <si>
+    <t>0.678 ± 0.011</t>
+  </si>
+  <si>
+    <t>23.258 ± 0.142</t>
+  </si>
+  <si>
+    <t>33.488 ± 0.247</t>
+  </si>
+  <si>
+    <t>0.705 ± 0.005</t>
+  </si>
+  <si>
+    <t>0.840 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.837 ± 0.002</t>
+  </si>
+  <si>
+    <t>47.044 ± 2.790</t>
+  </si>
+  <si>
+    <t>61.794 ± 3.600</t>
+  </si>
+  <si>
+    <t>0.084 ± 0.030</t>
+  </si>
+  <si>
+    <t>0.286 ± 0.054</t>
+  </si>
+  <si>
+    <t>0.297 ± 0.054</t>
+  </si>
+  <si>
+    <t>33.225 ± 0.594</t>
+  </si>
+  <si>
+    <t>44.366  ± 0.928</t>
+  </si>
+  <si>
+    <t>0.476  ± 0.012</t>
+  </si>
+  <si>
+    <t>0.690  ± 0.009</t>
+  </si>
+  <si>
+    <t>0.686  ± 0.008</t>
+  </si>
+  <si>
+    <t>23.37 ± 0.129</t>
+  </si>
+  <si>
+    <t>33.624 ± 0.214</t>
+  </si>
+  <si>
+    <t>0.703 ± 0.005</t>
+  </si>
+  <si>
+    <t>0.839 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.835 ± 0.003</t>
+  </si>
+  <si>
+    <t>46.674 ± 2.997</t>
+  </si>
+  <si>
+    <t>61.667 ± 3.989</t>
+  </si>
+  <si>
+    <t>0.089 ± 0.014</t>
+  </si>
+  <si>
+    <t>0.297 ± 0.024</t>
+  </si>
+  <si>
+    <t>0.301 ± 0.033</t>
+  </si>
+  <si>
+    <t>33.089 ± 0.590</t>
+  </si>
+  <si>
+    <t>44.216 ± 0.985</t>
+  </si>
+  <si>
+    <t>0.485 ± 0.010</t>
+  </si>
+  <si>
+    <t>0.697 ± 0.007</t>
+  </si>
+  <si>
+    <t>0.690 ± 0.006</t>
+  </si>
+  <si>
+    <t>23.326 ± 0.161</t>
+  </si>
+  <si>
+    <t>33.602 ± 0.221</t>
+  </si>
+  <si>
+    <t>0.707 ± 0.004</t>
+  </si>
+  <si>
+    <t>48.015 ± 3.179</t>
+  </si>
+  <si>
+    <t>63.635 ± 4.291</t>
+  </si>
+  <si>
+    <t>0.052 ± 0.024</t>
+  </si>
+  <si>
+    <t>0.223 ± 0.053</t>
+  </si>
+  <si>
+    <t>0.254 ± 0.047</t>
+  </si>
+  <si>
+    <t>31.859 ± 0.552</t>
+  </si>
+  <si>
+    <t>42.603 ± 1.115</t>
+  </si>
+  <si>
+    <t>0.514 ± 0.015</t>
+  </si>
+  <si>
+    <t>0.717 ± 0.010</t>
+  </si>
+  <si>
+    <t>0.714 ± 0.007</t>
+  </si>
+  <si>
+    <t>GAT+FFNN</t>
+  </si>
+  <si>
+    <t>27.237 ± 0.140</t>
+  </si>
+  <si>
+    <t>37.224 ± 0.168</t>
+  </si>
+  <si>
+    <t>0.643 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.802 ± 0.002</t>
+  </si>
+  <si>
+    <t>48.977 ± 3.232</t>
+  </si>
+  <si>
+    <t>65.071 ± 4.397</t>
+  </si>
+  <si>
+    <t>0.119 ± 0.017</t>
+  </si>
+  <si>
+    <t>0.222 ± 0.071</t>
+  </si>
+  <si>
+    <t>0.274 ± 0.063</t>
+  </si>
+  <si>
+    <t>36.853 ± 0.633</t>
+  </si>
+  <si>
+    <t>48.763 ± 0.996</t>
+  </si>
+  <si>
+    <t>0.370 ± 0.016</t>
+  </si>
+  <si>
+    <t>0.608 ± 0.013</t>
+  </si>
+  <si>
+    <t>0.593 ± 0.011</t>
+  </si>
+  <si>
+    <t>26.249 ± 0.169</t>
+  </si>
+  <si>
+    <t>36.730 ± 0.202</t>
+  </si>
+  <si>
+    <t>0.657 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.810 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.807 ± 0.002</t>
+  </si>
+  <si>
+    <t>47.626 ± 2.676</t>
+  </si>
+  <si>
+    <t>62.749 ± 3.543</t>
+  </si>
+  <si>
+    <t>0.070 ± 0.030</t>
+  </si>
+  <si>
+    <t>0.259 ± 0.060</t>
+  </si>
+  <si>
+    <t>0.279 ± 0.063</t>
+  </si>
+  <si>
+    <t>37.671 ± 0.933</t>
+  </si>
+  <si>
+    <t>49.766 ± 1.288</t>
+  </si>
+  <si>
+    <t>0.329 ± 0.020</t>
+  </si>
+  <si>
+    <t>0.573 ± 0.017</t>
+  </si>
+  <si>
+    <t>0.580 ± 0.018</t>
+  </si>
+  <si>
+    <t>25.755 ± 0.106</t>
+  </si>
+  <si>
+    <t>36.017 ± 0.124</t>
+  </si>
+  <si>
+    <t>0.678 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.823 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.822 ± 0.002</t>
+  </si>
+  <si>
+    <t>48.967 ± 2.838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.494 ± 4.206 </t>
+  </si>
+  <si>
+    <t>0.026 ± 0.020</t>
+  </si>
+  <si>
+    <t>0.151 ± 0.068</t>
+  </si>
+  <si>
+    <t>0.178 ± 0.053</t>
+  </si>
+  <si>
+    <t>36.803 ± 1.001</t>
+  </si>
+  <si>
+    <t>48.879 ± 1.261</t>
+  </si>
+  <si>
+    <t>0.370 ± 0.020</t>
+  </si>
+  <si>
+    <t>0.608 ± 0.016</t>
+  </si>
+  <si>
+    <t>0.584 ± 0.015</t>
+  </si>
+  <si>
+    <t>26.629 ± 0.091</t>
+  </si>
+  <si>
+    <t>36.751 ± 0.140</t>
+  </si>
+  <si>
+    <t>0.662 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.813 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.811 ± 0.002</t>
+  </si>
+  <si>
+    <t>49.557 ± 3.327</t>
+  </si>
+  <si>
+    <t>65.330 ± 4.349</t>
+  </si>
+  <si>
+    <t>0.050 ± 0.050</t>
+  </si>
+  <si>
+    <t>0.155 ± 0.041</t>
+  </si>
+  <si>
+    <t>0.201 ± 0.056</t>
+  </si>
+  <si>
+    <t>35.158 ± 0.803</t>
+  </si>
+  <si>
+    <t>45.068 ± 0.951</t>
+  </si>
+  <si>
+    <t>0.483 ± 0.010</t>
+  </si>
+  <si>
+    <t>0.695 ± 0.008</t>
+  </si>
+  <si>
+    <t>0.682 ± 0.005</t>
+  </si>
+  <si>
+    <t>GCN+FFNN</t>
+  </si>
+  <si>
+    <t>23.331 ± 0.077</t>
+  </si>
+  <si>
+    <t>33.621 ± 0.182</t>
+  </si>
+  <si>
+    <t>0.709 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.842 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.838 ± 0.002</t>
+  </si>
+  <si>
+    <t>47.660 ± 3.111</t>
+  </si>
+  <si>
+    <t>64.093 ± 4.192</t>
+  </si>
+  <si>
+    <t>0.185 ± 0.048</t>
+  </si>
+  <si>
+    <t>0.383 ± 0.078</t>
+  </si>
+  <si>
+    <t>0.441 ± 0.053</t>
+  </si>
+  <si>
+    <t>33.307 ± 0.703</t>
+  </si>
+  <si>
+    <t>44.691 ± 1.269</t>
+  </si>
+  <si>
+    <t>0.468 ± 0.018</t>
+  </si>
+  <si>
+    <t>0.684 ± 0.013</t>
+  </si>
+  <si>
+    <t>0.672 ± 0.011</t>
+  </si>
+  <si>
+    <t>23.655 ± 0.095</t>
+  </si>
+  <si>
+    <t>33.910 ± 0.155</t>
+  </si>
+  <si>
+    <t>0.703 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.836 ± 0.002</t>
+  </si>
+  <si>
+    <t>48.399 ± 3.128</t>
+  </si>
+  <si>
+    <t>63.499 ± 4.226</t>
+  </si>
+  <si>
+    <t>0.060 ± 0.024</t>
+  </si>
+  <si>
+    <t>0.240 ± 0.050</t>
+  </si>
+  <si>
+    <t>0.264 ± 0.046</t>
+  </si>
+  <si>
+    <t>33.254 ± 0.562</t>
+  </si>
+  <si>
+    <t>44.653 ± 1.091</t>
+  </si>
+  <si>
+    <t>0.466 ± 0.018</t>
+  </si>
+  <si>
+    <t>0.683 ± 0.013</t>
+  </si>
+  <si>
+    <t>0.667 ± 0.012</t>
+  </si>
+  <si>
+    <t>23.303 ± 0.081</t>
+  </si>
+  <si>
+    <t>33.622  ± 0.116</t>
+  </si>
+  <si>
+    <t>0.709  ± 0.001</t>
+  </si>
+  <si>
+    <t>0.842  ± 0.001</t>
+  </si>
+  <si>
+    <t>0.842  ± 0.002</t>
+  </si>
+  <si>
+    <t>48.738 ± 2.948</t>
+  </si>
+  <si>
+    <t>63.904 ± 4.504</t>
+  </si>
+  <si>
+    <t>0.038 ± 0.033</t>
+  </si>
+  <si>
+    <t>0.163 ± 0.118</t>
+  </si>
+  <si>
+    <t>0.172 ± 0.093</t>
+  </si>
+  <si>
+    <t>32.794 ± 0.604</t>
+  </si>
+  <si>
+    <t>44.121 ± 1.216</t>
+  </si>
+  <si>
+    <t>0.479 ± 0.018</t>
+  </si>
+  <si>
+    <t>0.692 ± 0.013</t>
+  </si>
+  <si>
+    <t>0.679 ± 0.010</t>
+  </si>
+  <si>
+    <t>22.767 ± 0.067</t>
+  </si>
+  <si>
+    <t>32.884 ± 0.132</t>
+  </si>
+  <si>
+    <t>0.723 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.851 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.849 ± 0.002</t>
+  </si>
+  <si>
+    <t>46.398 ± 3.159</t>
+  </si>
+  <si>
+    <t>62.160 ± 4.813</t>
+  </si>
+  <si>
+    <t>0.072 ± 0.040</t>
+  </si>
+  <si>
+    <t>0.262 ± 0.068</t>
+  </si>
+  <si>
+    <t>0.310 ± 0.042</t>
+  </si>
+  <si>
+    <t>32.547 ± 0.567</t>
+  </si>
+  <si>
+    <t>43.910 ± 1.059</t>
+  </si>
+  <si>
+    <t>0.485 ± 0.014</t>
+  </si>
+  <si>
+    <t>0.696 ± 0.010</t>
+  </si>
+  <si>
+    <t>0.683 ± 0.009</t>
+  </si>
+  <si>
+    <t>Drug Features</t>
+  </si>
+  <si>
+    <t>Patient Features</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Clinical_CellType_Module</t>
+  </si>
+  <si>
+    <t>32.499 +/- 0.427</t>
+  </si>
+  <si>
+    <t>44.162 +/- 1.061</t>
+  </si>
+  <si>
+    <t>0.488 +/- 0.013</t>
+  </si>
+  <si>
+    <t>0.699 +/- 0.009</t>
+  </si>
+  <si>
+    <t>0.695 +/- 0.014</t>
+  </si>
+  <si>
+    <t>KD Embed</t>
+  </si>
+  <si>
+    <t>32.706 +/- 0.766</t>
+  </si>
+  <si>
+    <t>44.241 +/- 0.815</t>
+  </si>
+  <si>
+    <t>0.489 +/- 0.011</t>
+  </si>
+  <si>
+    <t>0.699 +/- 0.008</t>
+  </si>
+  <si>
+    <t>0.695 +/- 0.013</t>
+  </si>
+  <si>
+    <t>KD Embed + PC</t>
+  </si>
+  <si>
+    <t>32.704 +/- 2.419</t>
+  </si>
+  <si>
+    <t>44.192 +/- 3.918</t>
+  </si>
+  <si>
+    <t>0.492 +/- 0.059</t>
+  </si>
+  <si>
+    <t>0.700 +/- 0.043</t>
+  </si>
+  <si>
+    <t>0.693 +/- 0.036</t>
+  </si>
+  <si>
+    <t>Gene Expr</t>
+  </si>
+  <si>
+    <t>31.552 +/- 1.995</t>
+  </si>
+  <si>
+    <t>43.097 +/- 3.200</t>
+  </si>
+  <si>
+    <t>0.516 +/- 0.055</t>
+  </si>
+  <si>
+    <t>0.717 +/- 0.038</t>
+  </si>
+  <si>
+    <t>0.711 +/- 0.035</t>
+  </si>
+  <si>
+    <t>31.376 +/- 1.362</t>
+  </si>
+  <si>
+    <t>43.060 +/- 2.418</t>
+  </si>
+  <si>
+    <t>0.516 +/- 0.033</t>
+  </si>
+  <si>
+    <t>0.718 +/- 0.023</t>
+  </si>
+  <si>
+    <t>0.713 +/- 0.022</t>
+  </si>
+  <si>
+    <t>31.545 +/- 1.402</t>
+  </si>
+  <si>
+    <t>42.869 +/- 2.137</t>
+  </si>
+  <si>
+    <t>0.516 +/- 0.037</t>
+  </si>
+  <si>
+    <t>0.718 +/- 0.025</t>
+  </si>
+  <si>
+    <t>0.712 +/- 0.020</t>
+  </si>
+  <si>
+    <t>Mutation</t>
+  </si>
+  <si>
+    <t>34.675 +/- 2.152</t>
+  </si>
+  <si>
+    <t>46.791 +/- 2.389</t>
+  </si>
+  <si>
+    <t>0.434 +/- 0.032</t>
+  </si>
+  <si>
+    <t>0.658 +/- 0.024</t>
+  </si>
+  <si>
+    <t>0.658 +/- 0.028</t>
+  </si>
+  <si>
+    <t>34.553 +/- 1.328</t>
+  </si>
+  <si>
+    <t>46.800 +/- 2.485</t>
+  </si>
+  <si>
+    <t>0.435 +/- 0.030</t>
+  </si>
+  <si>
+    <t>0.659 +/- 0.023</t>
+  </si>
+  <si>
+    <t>0.659 +/- 0.018</t>
+  </si>
+  <si>
+    <t>34.464 +/- 1.620</t>
+  </si>
+  <si>
+    <t>46.491 +/- 2.692</t>
+  </si>
+  <si>
+    <t>0.438 +/- 0.037</t>
+  </si>
+  <si>
+    <t>0.662 +/- 0.028</t>
+  </si>
+  <si>
+    <t>0.660 +/- 0.023</t>
+  </si>
+  <si>
+    <t>Pathways</t>
+  </si>
+  <si>
+    <t>33.179 +/- 1.827</t>
+  </si>
+  <si>
+    <t>44.728 +/- 3.273</t>
+  </si>
+  <si>
+    <t>0.479 +/- 0.038</t>
+  </si>
+  <si>
+    <t>0.691 +/- 0.028</t>
+  </si>
+  <si>
+    <t>0.683 +/- 0.021</t>
+  </si>
+  <si>
+    <t>32.916 +/- 1.116</t>
+  </si>
+  <si>
+    <t>44.596 +/- 2.123</t>
+  </si>
+  <si>
+    <t>0.482 +/- 0.034</t>
+  </si>
+  <si>
+    <t>0.694 +/- 0.025</t>
+  </si>
+  <si>
+    <t>0.688 +/- 0.020</t>
+  </si>
+  <si>
+    <t>32.748 +/- 1.793</t>
+  </si>
+  <si>
+    <t>44.307 +/- 3.121</t>
+  </si>
+  <si>
+    <t>0.487 +/- 0.042</t>
+  </si>
+  <si>
+    <t>0.697 +/- 0.030</t>
+  </si>
+  <si>
+    <t>0.690 +/- 0.024</t>
+  </si>
+  <si>
+    <t>Clinical_CellType_Module + Gene Expr</t>
+  </si>
+  <si>
+    <t>31.524 +/- 1.461</t>
+  </si>
+  <si>
+    <t>43.150 +/- 2.484</t>
+  </si>
+  <si>
+    <t>0.513 +/- 0.026</t>
+  </si>
+  <si>
+    <t>0.716 +/- 0.018</t>
+  </si>
+  <si>
+    <t>0.708 +/- 0.014</t>
+  </si>
+  <si>
+    <t>31.128 +/- 1.500</t>
+  </si>
+  <si>
+    <t>42.862 +/- 2.267</t>
+  </si>
+  <si>
+    <t>0.520 +/- 0.037</t>
+  </si>
+  <si>
+    <t>0.720 +/- 0.026</t>
+  </si>
+  <si>
+    <t>0.715 +/- 0.027</t>
+  </si>
+  <si>
+    <t>31.358 +/- 0.877</t>
+  </si>
+  <si>
+    <t>43.056 +/- 2.004</t>
+  </si>
+  <si>
+    <t>0.516 +/- 0.029</t>
+  </si>
+  <si>
+    <t>0.718 +/- 0.021</t>
+  </si>
+  <si>
+    <t>0.713 +/- 0.009</t>
+  </si>
+  <si>
+    <t>Clinical_CellType_Module + Mutation</t>
+  </si>
+  <si>
+    <t>32.293 +/- 2.316</t>
+  </si>
+  <si>
+    <t>43.955 +/- 3.477</t>
+  </si>
+  <si>
+    <t>0.493 +/- 0.044</t>
+  </si>
+  <si>
+    <t>0.702 +/- 0.031</t>
+  </si>
+  <si>
+    <t>0.698 +/- 0.024</t>
+  </si>
+  <si>
+    <t>32.639 +/- 1.948</t>
+  </si>
+  <si>
+    <t>44.334 +/- 3.237</t>
+  </si>
+  <si>
+    <t>0.487 +/- 0.037</t>
+  </si>
+  <si>
+    <t>0.697 +/- 0.027</t>
+  </si>
+  <si>
+    <t>0.693 +/- 0.021</t>
+  </si>
+  <si>
+    <t>32.182 +/- 1.357</t>
+  </si>
+  <si>
+    <t>43.864 +/- 2.656</t>
+  </si>
+  <si>
+    <t>0.497 +/- 0.041</t>
+  </si>
+  <si>
+    <t>0.704 +/- 0.030</t>
+  </si>
+  <si>
+    <t>0.701 +/- 0.017</t>
+  </si>
+  <si>
+    <t>Clinical_CellType_Module + Pathways</t>
+  </si>
+  <si>
+    <t>32.281 +/- 1.839</t>
+  </si>
+  <si>
+    <t>44.051 +/- 3.463</t>
+  </si>
+  <si>
+    <t>0.491 +/- 0.035</t>
+  </si>
+  <si>
+    <t>0.700 +/- 0.025</t>
+  </si>
+  <si>
+    <t>0.694 +/- 0.015</t>
+  </si>
+  <si>
+    <t>32.263 +/- 0.481</t>
+  </si>
+  <si>
+    <t>43.787 +/- 1.517</t>
+  </si>
+  <si>
+    <t>0.497 +/- 0.021</t>
+  </si>
+  <si>
+    <t>0.705 +/- 0.015</t>
+  </si>
+  <si>
+    <t>0.697 +/- 0.016</t>
+  </si>
+  <si>
+    <t>32.419 +/- 1.452</t>
+  </si>
+  <si>
+    <t>44.066 +/- 2.229</t>
+  </si>
+  <si>
+    <t>0.490 +/- 0.039</t>
+  </si>
+  <si>
+    <t>0.700 +/- 0.027</t>
+  </si>
+  <si>
+    <t>0.695 +/- 0.027</t>
+  </si>
+  <si>
+    <t>Gene Expr + Mutation</t>
+  </si>
+  <si>
+    <t>31.480 +/- 0.982</t>
+  </si>
+  <si>
+    <t>43.085 +/- 1.842</t>
+  </si>
+  <si>
+    <t>0.513 +/- 0.033</t>
+  </si>
+  <si>
+    <t>0.716 +/- 0.023</t>
+  </si>
+  <si>
+    <t>0.710 +/- 0.021</t>
+  </si>
+  <si>
+    <t>31.210 +/- 1.213</t>
+  </si>
+  <si>
+    <t>42.732 +/- 1.990</t>
+  </si>
+  <si>
+    <t>0.521 +/- 0.025</t>
+  </si>
+  <si>
+    <t>0.721 +/- 0.017</t>
+  </si>
+  <si>
+    <t>0.716 +/- 0.020</t>
+  </si>
+  <si>
+    <t>31.535 +/- 1.505</t>
+  </si>
+  <si>
+    <t>43.145 +/- 2.130</t>
+  </si>
+  <si>
+    <t>0.513 +/- 0.030</t>
+  </si>
+  <si>
+    <t>0.716 +/- 0.021</t>
+  </si>
+  <si>
+    <t>0.709 +/- 0.020</t>
+  </si>
+  <si>
+    <t>Gene Expr + Pathways</t>
+  </si>
+  <si>
+    <t>31.483 +/- 0.670</t>
+  </si>
+  <si>
+    <t>43.031 +/- 0.969</t>
+  </si>
+  <si>
+    <t>0.515 +/- 0.014</t>
+  </si>
+  <si>
+    <t>0.718 +/- 0.010</t>
   </si>
   <si>
     <t>0.711 +/- 0.013</t>
   </si>
   <si>
-    <t>26.009 +/- 0.266</t>
-  </si>
-  <si>
-    <t>36.423 +/- 0.249</t>
-  </si>
-  <si>
-    <t>0.651 +/- 0.003</t>
-  </si>
-  <si>
-    <t>45.285 +/- 3.859</t>
-  </si>
-  <si>
-    <t>57.409 +/- 4.639</t>
-  </si>
-  <si>
-    <t>0.150 +/- 0.065</t>
-  </si>
-  <si>
-    <t>0.377 +/- 0.088</t>
-  </si>
-  <si>
-    <t>0.348 +/- 0.096</t>
-  </si>
-  <si>
-    <t>31.574 +/- 1.417</t>
-  </si>
-  <si>
-    <t>43.230 +/- 1.860</t>
-  </si>
-  <si>
-    <t>0.512 +/- 0.032</t>
-  </si>
-  <si>
-    <t>0.715 +/- 0.022</t>
-  </si>
-  <si>
-    <t>0.709 +/- 0.028</t>
-  </si>
-  <si>
-    <t>25.995 +/- 0.259</t>
-  </si>
-  <si>
-    <t>36.373 +/- 0.219</t>
-  </si>
-  <si>
-    <t>0.652 +/- 0.003</t>
-  </si>
-  <si>
-    <t>0.808 +/- 0.001</t>
-  </si>
-  <si>
-    <t>45.227 +/- 1.978</t>
-  </si>
-  <si>
-    <t>57.499 +/- 3.396</t>
-  </si>
-  <si>
-    <t>0.139 +/- 0.019</t>
-  </si>
-  <si>
-    <t>0.372 +/- 0.024</t>
-  </si>
-  <si>
-    <t>0.346 +/- 0.030</t>
-  </si>
-  <si>
-    <t>31.592 +/- 1.327</t>
-  </si>
-  <si>
-    <t>43.138 +/- 2.793</t>
-  </si>
-  <si>
-    <t>0.513 +/- 0.034</t>
-  </si>
-  <si>
-    <t>0.716 +/- 0.024</t>
-  </si>
-  <si>
-    <t>0.708 +/- 0.019</t>
-  </si>
-  <si>
-    <t>CNN</t>
-  </si>
-  <si>
-    <t>23.039 ± 0.161</t>
-  </si>
-  <si>
-    <t>33.460 ± 0.188</t>
-  </si>
-  <si>
-    <t>0.708 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.841 ± 0.002</t>
-  </si>
-  <si>
-    <t>0.839 ± 0.001</t>
-  </si>
-  <si>
-    <t>49.872 ± 3.180</t>
-  </si>
-  <si>
-    <t>65.263 ± 4.417</t>
-  </si>
-  <si>
-    <t>0.170 ± 0.034</t>
-  </si>
-  <si>
-    <t>0.358 ± 0.065</t>
-  </si>
-  <si>
-    <t>0.366 ± 0.050</t>
-  </si>
-  <si>
-    <t>32.174 ± 0.756</t>
-  </si>
-  <si>
-    <t>42.891 ± 1.195</t>
-  </si>
-  <si>
-    <t>0.500 ± 0.017</t>
-  </si>
-  <si>
-    <t>0.707 ± 0.012</t>
-  </si>
-  <si>
-    <t>0.704 ± 0.011</t>
-  </si>
-  <si>
-    <t>22.883 ± 0.152</t>
-  </si>
-  <si>
-    <t>33.260 ± 0.251</t>
-  </si>
-  <si>
-    <t>0.711 ± 0.005</t>
-  </si>
-  <si>
-    <t>0.843 ± 0.003</t>
-  </si>
-  <si>
-    <t>51.028 ± 2.534</t>
-  </si>
-  <si>
-    <t>65.739 ± 3.695</t>
-  </si>
-  <si>
-    <t>0.003 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.025 ± 0.057</t>
-  </si>
-  <si>
-    <t>0.070 ±0.059</t>
-  </si>
-  <si>
-    <t>34.225 ± 0.582</t>
-  </si>
-  <si>
-    <t>44.239 ± 0.941</t>
-  </si>
-  <si>
-    <t>0.504 ± 0.014</t>
-  </si>
-  <si>
-    <t>0.710 ± 0.010</t>
-  </si>
-  <si>
-    <t>0.701 ± 0.008</t>
-  </si>
-  <si>
-    <t>22.946 ± 0.170</t>
-  </si>
-  <si>
-    <t>33.250 ± 0.206</t>
-  </si>
-  <si>
-    <t>0.711 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.840 ± 0.002</t>
-  </si>
-  <si>
-    <t>49.115 ± 2.833</t>
-  </si>
-  <si>
-    <t>66.549 ± 4.753</t>
-  </si>
-  <si>
-    <t>0.059 ±  0.034</t>
-  </si>
-  <si>
-    <t>0.234 ± 0.070</t>
-  </si>
-  <si>
-    <t>0.259 ± 0.045</t>
-  </si>
-  <si>
-    <t>31.466 ± 0.545</t>
-  </si>
-  <si>
-    <t>41.847 ± 1.145</t>
-  </si>
-  <si>
-    <t>0.528 ± 0.016</t>
-  </si>
-  <si>
-    <t>0.726 ± 0.011</t>
-  </si>
-  <si>
-    <t>0.719 ± 0.008</t>
-  </si>
-  <si>
-    <t>22.758 ± 0.157</t>
-  </si>
-  <si>
-    <t>32.757 ± 0.246</t>
-  </si>
-  <si>
-    <t>0.718 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.848 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.844 ± 0.002</t>
-  </si>
-  <si>
-    <t>49.096 ± 2.723</t>
-  </si>
-  <si>
-    <t>64.816 ± 4.040</t>
-  </si>
-  <si>
-    <t>0.065 ± 0.031</t>
-  </si>
-  <si>
-    <t>0.249 ± 0.063</t>
-  </si>
-  <si>
-    <t>0.244 ± 0.052</t>
-  </si>
-  <si>
-    <t>32.106 ± 0.498</t>
-  </si>
-  <si>
-    <t>43.058 ± 1.107</t>
-  </si>
-  <si>
-    <t>0.506 ± 0.014</t>
-  </si>
-  <si>
-    <t>0.711 ± 0.010</t>
-  </si>
-  <si>
-    <t>0.701 ± 0.007</t>
-  </si>
-  <si>
-    <t>LSTM</t>
-  </si>
-  <si>
-    <t>23.528 ± 0.166</t>
-  </si>
-  <si>
-    <t>33.527 ± 0.229</t>
-  </si>
-  <si>
-    <t>0.705 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.834 ± 0.002</t>
-  </si>
-  <si>
-    <t>46.551 ± 3.168</t>
-  </si>
-  <si>
-    <t>62.456 ± 4.331</t>
-  </si>
-  <si>
-    <t>0.183 ± 0.031</t>
-  </si>
-  <si>
-    <t>0.383 ± 0.054</t>
-  </si>
-  <si>
-    <t>0.419 ± 0.047</t>
-  </si>
-  <si>
-    <t>33.370 ± 0.582</t>
-  </si>
-  <si>
-    <t>44.839 ± 0.853</t>
-  </si>
-  <si>
-    <t>0.460 ± 0.011</t>
-  </si>
-  <si>
-    <t>0.678 ± 0.008</t>
-  </si>
-  <si>
-    <t>0.678 ± 0.011</t>
-  </si>
-  <si>
-    <t>23.258 ± 0.142</t>
-  </si>
-  <si>
-    <t>33.488 ± 0.247</t>
-  </si>
-  <si>
-    <t>0.705 ± 0.005</t>
-  </si>
-  <si>
-    <t>0.840 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.837 ± 0.002</t>
-  </si>
-  <si>
-    <t>47.044 ± 2.790</t>
-  </si>
-  <si>
-    <t>61.794 ± 3.600</t>
-  </si>
-  <si>
-    <t>0.084 ± 0.030</t>
-  </si>
-  <si>
-    <t>0.286 ± 0.054</t>
-  </si>
-  <si>
-    <t>0.297 ± 0.054</t>
-  </si>
-  <si>
-    <t>33.225 ± 0.594</t>
-  </si>
-  <si>
-    <t>44.366  ± 0.928</t>
-  </si>
-  <si>
-    <t>0.476  ± 0.012</t>
-  </si>
-  <si>
-    <t>0.690  ± 0.009</t>
-  </si>
-  <si>
-    <t>0.686  ± 0.008</t>
-  </si>
-  <si>
-    <t>23.37 ± 0.129</t>
-  </si>
-  <si>
-    <t>33.624 ± 0.214</t>
-  </si>
-  <si>
-    <t>0.703 ± 0.005</t>
-  </si>
-  <si>
-    <t>0.839 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.835 ± 0.003</t>
-  </si>
-  <si>
-    <t>46.674 ± 2.997</t>
-  </si>
-  <si>
-    <t>61.667 ± 3.989</t>
-  </si>
-  <si>
-    <t>0.089 ± 0.014</t>
-  </si>
-  <si>
-    <t>0.297 ± 0.024</t>
-  </si>
-  <si>
-    <t>0.301 ± 0.033</t>
-  </si>
-  <si>
-    <t>33.089 ± 0.590</t>
-  </si>
-  <si>
-    <t>44.216 ± 0.985</t>
-  </si>
-  <si>
-    <t>0.485 ± 0.010</t>
-  </si>
-  <si>
-    <t>0.697 ± 0.007</t>
-  </si>
-  <si>
-    <t>0.690 ± 0.006</t>
-  </si>
-  <si>
-    <t>23.326 ± 0.161</t>
-  </si>
-  <si>
-    <t>33.602 ± 0.221</t>
-  </si>
-  <si>
-    <t>0.707 ± 0.004</t>
-  </si>
-  <si>
-    <t>48.015 ± 3.179</t>
-  </si>
-  <si>
-    <t>63.635 ± 4.291</t>
-  </si>
-  <si>
-    <t>0.052 ± 0.024</t>
-  </si>
-  <si>
-    <t>0.223 ± 0.053</t>
-  </si>
-  <si>
-    <t>0.254 ± 0.047</t>
-  </si>
-  <si>
-    <t>31.859 ± 0.552</t>
-  </si>
-  <si>
-    <t>42.603 ± 1.115</t>
-  </si>
-  <si>
-    <t>0.514 ± 0.015</t>
-  </si>
-  <si>
-    <t>0.717 ± 0.010</t>
-  </si>
-  <si>
-    <t>0.714 ± 0.007</t>
-  </si>
-  <si>
-    <t>GAT+FFNN</t>
-  </si>
-  <si>
-    <t>27.237 ± 0.140</t>
-  </si>
-  <si>
-    <t>37.224 ± 0.168</t>
-  </si>
-  <si>
-    <t>0.643 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.802 ± 0.002</t>
-  </si>
-  <si>
-    <t>48.977 ± 3.232</t>
-  </si>
-  <si>
-    <t>65.071 ± 4.397</t>
-  </si>
-  <si>
-    <t>0.119 ± 0.017</t>
-  </si>
-  <si>
-    <t>0.222 ± 0.071</t>
-  </si>
-  <si>
-    <t>0.274 ± 0.063</t>
-  </si>
-  <si>
-    <t>36.853 ± 0.633</t>
-  </si>
-  <si>
-    <t>48.763 ± 0.996</t>
-  </si>
-  <si>
-    <t>0.370 ± 0.016</t>
-  </si>
-  <si>
-    <t>0.608 ± 0.013</t>
-  </si>
-  <si>
-    <t>0.593 ± 0.011</t>
-  </si>
-  <si>
-    <t>26.249 ± 0.169</t>
-  </si>
-  <si>
-    <t>36.730 ± 0.202</t>
-  </si>
-  <si>
-    <t>0.657 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.810 ± 0.002</t>
-  </si>
-  <si>
-    <t>0.807 ± 0.002</t>
-  </si>
-  <si>
-    <t>47.626 ± 2.676</t>
-  </si>
-  <si>
-    <t>62.749 ± 3.543</t>
-  </si>
-  <si>
-    <t>0.070 ± 0.030</t>
-  </si>
-  <si>
-    <t>0.259 ± 0.060</t>
-  </si>
-  <si>
-    <t>0.279 ± 0.063</t>
-  </si>
-  <si>
-    <t>37.671 ± 0.933</t>
-  </si>
-  <si>
-    <t>49.766 ± 1.288</t>
-  </si>
-  <si>
-    <t>0.329 ± 0.020</t>
-  </si>
-  <si>
-    <t>0.573 ± 0.017</t>
-  </si>
-  <si>
-    <t>0.580 ± 0.018</t>
-  </si>
-  <si>
-    <t>25.755 ± 0.106</t>
-  </si>
-  <si>
-    <t>36.017 ± 0.124</t>
-  </si>
-  <si>
-    <t>0.678 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.823 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.822 ± 0.002</t>
-  </si>
-  <si>
-    <t>48.967 ± 2.838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.494 ± 4.206 </t>
-  </si>
-  <si>
-    <t>0.026 ± 0.020</t>
-  </si>
-  <si>
-    <t>0.151 ± 0.068</t>
-  </si>
-  <si>
-    <t>0.178 ± 0.053</t>
-  </si>
-  <si>
-    <t>36.803 ± 1.001</t>
-  </si>
-  <si>
-    <t>48.879 ± 1.261</t>
-  </si>
-  <si>
-    <t>0.370 ± 0.020</t>
-  </si>
-  <si>
-    <t>0.608 ± 0.016</t>
-  </si>
-  <si>
-    <t>0.584 ± 0.015</t>
-  </si>
-  <si>
-    <t>26.629 ± 0.091</t>
-  </si>
-  <si>
-    <t>36.751 ± 0.140</t>
-  </si>
-  <si>
-    <t>0.662 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.813 ± 0.002</t>
-  </si>
-  <si>
-    <t>0.811 ± 0.002</t>
-  </si>
-  <si>
-    <t>49.557 ± 3.327</t>
-  </si>
-  <si>
-    <t>65.330 ± 4.349</t>
-  </si>
-  <si>
-    <t>0.050 ± 0.050</t>
-  </si>
-  <si>
-    <t>0.155 ± 0.041</t>
-  </si>
-  <si>
-    <t>0.201 ± 0.056</t>
-  </si>
-  <si>
-    <t>35.158 ± 0.803</t>
-  </si>
-  <si>
-    <t>45.068 ± 0.951</t>
-  </si>
-  <si>
-    <t>0.483 ± 0.010</t>
-  </si>
-  <si>
-    <t>0.695 ± 0.008</t>
-  </si>
-  <si>
-    <t>0.682 ± 0.005</t>
-  </si>
-  <si>
-    <t>GCN+FFNN</t>
-  </si>
-  <si>
-    <t>23.331 ± 0.077</t>
-  </si>
-  <si>
-    <t>33.621 ± 0.182</t>
-  </si>
-  <si>
-    <t>0.709 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.842 ± 0.002</t>
-  </si>
-  <si>
-    <t>0.838 ± 0.002</t>
-  </si>
-  <si>
-    <t>47.660 ± 3.111</t>
-  </si>
-  <si>
-    <t>64.093 ± 4.192</t>
-  </si>
-  <si>
-    <t>0.185 ± 0.048</t>
-  </si>
-  <si>
-    <t>0.383 ± 0.078</t>
-  </si>
-  <si>
-    <t>0.441 ± 0.053</t>
-  </si>
-  <si>
-    <t>33.307 ± 0.703</t>
-  </si>
-  <si>
-    <t>44.691 ± 1.269</t>
-  </si>
-  <si>
-    <t>0.468 ± 0.018</t>
-  </si>
-  <si>
-    <t>0.684 ± 0.013</t>
-  </si>
-  <si>
-    <t>0.672 ± 0.011</t>
-  </si>
-  <si>
-    <t>23.655 ± 0.095</t>
-  </si>
-  <si>
-    <t>33.910 ± 0.155</t>
-  </si>
-  <si>
-    <t>0.703 ± 0.002</t>
-  </si>
-  <si>
-    <t>0.836 ± 0.002</t>
-  </si>
-  <si>
-    <t>48.399 ± 3.128</t>
-  </si>
-  <si>
-    <t>63.499 ± 4.226</t>
-  </si>
-  <si>
-    <t>0.060 ± 0.024</t>
-  </si>
-  <si>
-    <t>0.240 ± 0.050</t>
-  </si>
-  <si>
-    <t>0.264 ± 0.046</t>
-  </si>
-  <si>
-    <t>33.254 ± 0.562</t>
-  </si>
-  <si>
-    <t>44.653 ± 1.091</t>
-  </si>
-  <si>
-    <t>0.466 ± 0.018</t>
-  </si>
-  <si>
-    <t>0.683 ± 0.013</t>
-  </si>
-  <si>
-    <t>0.667 ± 0.012</t>
-  </si>
-  <si>
-    <t>23.303 ± 0.081</t>
-  </si>
-  <si>
-    <t>33.622  ± 0.116</t>
-  </si>
-  <si>
-    <t>0.709  ± 0.001</t>
-  </si>
-  <si>
-    <t>0.842  ± 0.001</t>
-  </si>
-  <si>
-    <t>0.842  ± 0.002</t>
-  </si>
-  <si>
-    <t>48.738 ± 2.948</t>
-  </si>
-  <si>
-    <t>63.904 ± 4.504</t>
-  </si>
-  <si>
-    <t>0.038 ± 0.033</t>
-  </si>
-  <si>
-    <t>0.163 ± 0.118</t>
-  </si>
-  <si>
-    <t>0.172 ± 0.093</t>
-  </si>
-  <si>
-    <t>32.794 ± 0.604</t>
-  </si>
-  <si>
-    <t>44.121 ± 1.216</t>
-  </si>
-  <si>
-    <t>0.479 ± 0.018</t>
-  </si>
-  <si>
-    <t>0.692 ± 0.013</t>
-  </si>
-  <si>
-    <t>0.679 ± 0.010</t>
-  </si>
-  <si>
-    <t>22.767 ± 0.067</t>
-  </si>
-  <si>
-    <t>32.884 ± 0.132</t>
-  </si>
-  <si>
-    <t>0.723 ± 0.003</t>
-  </si>
-  <si>
-    <t>0.851 ± 0.002</t>
-  </si>
-  <si>
-    <t>0.849 ± 0.002</t>
-  </si>
-  <si>
-    <t>46.398 ± 3.159</t>
-  </si>
-  <si>
-    <t>62.160 ± 4.813</t>
-  </si>
-  <si>
-    <t>0.072 ± 0.040</t>
-  </si>
-  <si>
-    <t>0.262 ± 0.068</t>
-  </si>
-  <si>
-    <t>0.310 ± 0.042</t>
-  </si>
-  <si>
-    <t>32.547 ± 0.567</t>
-  </si>
-  <si>
-    <t>43.910 ± 1.059</t>
-  </si>
-  <si>
-    <t>0.485 ± 0.014</t>
-  </si>
-  <si>
-    <t>0.696 ± 0.010</t>
-  </si>
-  <si>
-    <t>0.683 ± 0.009</t>
-  </si>
-  <si>
-    <t>Drug Features</t>
-  </si>
-  <si>
-    <t>Patient Features</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Clinical_CellType_Module</t>
-  </si>
-  <si>
-    <t>32.499 +/- 0.427</t>
-  </si>
-  <si>
-    <t>44.162 +/- 1.061</t>
-  </si>
-  <si>
-    <t>0.488 +/- 0.013</t>
-  </si>
-  <si>
-    <t>0.699 +/- 0.009</t>
-  </si>
-  <si>
-    <t>0.695 +/- 0.014</t>
-  </si>
-  <si>
-    <t>KD Embed</t>
-  </si>
-  <si>
-    <t>32.706 +/- 0.766</t>
-  </si>
-  <si>
-    <t>44.241 +/- 0.815</t>
-  </si>
-  <si>
-    <t>0.489 +/- 0.011</t>
-  </si>
-  <si>
-    <t>0.699 +/- 0.008</t>
-  </si>
-  <si>
-    <t>0.695 +/- 0.013</t>
-  </si>
-  <si>
-    <t>KD Embed + PC</t>
-  </si>
-  <si>
-    <t>32.704 +/- 2.419</t>
-  </si>
-  <si>
-    <t>44.192 +/- 3.918</t>
-  </si>
-  <si>
-    <t>0.492 +/- 0.059</t>
-  </si>
-  <si>
-    <t>0.700 +/- 0.043</t>
-  </si>
-  <si>
-    <t>0.693 +/- 0.036</t>
-  </si>
-  <si>
-    <t>Gene Expr</t>
-  </si>
-  <si>
-    <t>31.552 +/- 1.995</t>
-  </si>
-  <si>
-    <t>43.097 +/- 3.200</t>
-  </si>
-  <si>
-    <t>0.516 +/- 0.055</t>
-  </si>
-  <si>
-    <t>0.717 +/- 0.038</t>
-  </si>
-  <si>
-    <t>0.711 +/- 0.035</t>
-  </si>
-  <si>
-    <t>31.376 +/- 1.362</t>
-  </si>
-  <si>
-    <t>43.060 +/- 2.418</t>
-  </si>
-  <si>
-    <t>0.516 +/- 0.033</t>
-  </si>
-  <si>
-    <t>0.718 +/- 0.023</t>
-  </si>
-  <si>
-    <t>0.713 +/- 0.022</t>
-  </si>
-  <si>
-    <t>31.545 +/- 1.402</t>
-  </si>
-  <si>
-    <t>42.869 +/- 2.137</t>
-  </si>
-  <si>
-    <t>0.516 +/- 0.037</t>
-  </si>
-  <si>
-    <t>0.718 +/- 0.025</t>
-  </si>
-  <si>
-    <t>0.712 +/- 0.020</t>
-  </si>
-  <si>
-    <t>Mutation</t>
-  </si>
-  <si>
-    <t>34.675 +/- 2.152</t>
-  </si>
-  <si>
-    <t>46.791 +/- 2.389</t>
-  </si>
-  <si>
-    <t>0.434 +/- 0.032</t>
-  </si>
-  <si>
-    <t>0.658 +/- 0.024</t>
-  </si>
-  <si>
-    <t>0.658 +/- 0.028</t>
-  </si>
-  <si>
-    <t>34.553 +/- 1.328</t>
-  </si>
-  <si>
-    <t>46.800 +/- 2.485</t>
-  </si>
-  <si>
-    <t>0.435 +/- 0.030</t>
-  </si>
-  <si>
-    <t>0.659 +/- 0.023</t>
-  </si>
-  <si>
-    <t>0.659 +/- 0.018</t>
-  </si>
-  <si>
-    <t>34.464 +/- 1.620</t>
-  </si>
-  <si>
-    <t>46.491 +/- 2.692</t>
-  </si>
-  <si>
-    <t>0.438 +/- 0.037</t>
-  </si>
-  <si>
-    <t>0.662 +/- 0.028</t>
-  </si>
-  <si>
-    <t>0.660 +/- 0.023</t>
-  </si>
-  <si>
-    <t>Pathways</t>
-  </si>
-  <si>
-    <t>33.179 +/- 1.827</t>
-  </si>
-  <si>
-    <t>44.728 +/- 3.273</t>
-  </si>
-  <si>
-    <t>0.479 +/- 0.038</t>
-  </si>
-  <si>
-    <t>0.691 +/- 0.028</t>
-  </si>
-  <si>
-    <t>0.683 +/- 0.021</t>
-  </si>
-  <si>
-    <t>32.916 +/- 1.116</t>
-  </si>
-  <si>
-    <t>44.596 +/- 2.123</t>
-  </si>
-  <si>
-    <t>0.482 +/- 0.034</t>
-  </si>
-  <si>
-    <t>0.694 +/- 0.025</t>
-  </si>
-  <si>
-    <t>0.688 +/- 0.020</t>
-  </si>
-  <si>
-    <t>32.748 +/- 1.793</t>
-  </si>
-  <si>
-    <t>44.307 +/- 3.121</t>
-  </si>
-  <si>
-    <t>0.487 +/- 0.042</t>
-  </si>
-  <si>
-    <t>0.697 +/- 0.030</t>
-  </si>
-  <si>
-    <t>0.690 +/- 0.024</t>
-  </si>
-  <si>
-    <t>Clinical_CellType_Module + Gene Expr</t>
-  </si>
-  <si>
-    <t>31.524 +/- 1.461</t>
-  </si>
-  <si>
-    <t>43.150 +/- 2.484</t>
-  </si>
-  <si>
-    <t>0.513 +/- 0.026</t>
-  </si>
-  <si>
-    <t>0.716 +/- 0.018</t>
-  </si>
-  <si>
-    <t>0.708 +/- 0.014</t>
-  </si>
-  <si>
-    <t>31.128 +/- 1.500</t>
-  </si>
-  <si>
-    <t>42.862 +/- 2.267</t>
-  </si>
-  <si>
-    <t>0.520 +/- 0.037</t>
-  </si>
-  <si>
-    <t>0.720 +/- 0.026</t>
-  </si>
-  <si>
-    <t>0.715 +/- 0.027</t>
-  </si>
-  <si>
-    <t>31.358 +/- 0.877</t>
-  </si>
-  <si>
-    <t>43.056 +/- 2.004</t>
-  </si>
-  <si>
-    <t>0.516 +/- 0.029</t>
-  </si>
-  <si>
-    <t>0.718 +/- 0.021</t>
-  </si>
-  <si>
-    <t>0.713 +/- 0.009</t>
-  </si>
-  <si>
-    <t>Clinical_CellType_Module + Mutation</t>
-  </si>
-  <si>
-    <t>32.293 +/- 2.316</t>
-  </si>
-  <si>
-    <t>43.955 +/- 3.477</t>
-  </si>
-  <si>
-    <t>0.493 +/- 0.044</t>
-  </si>
-  <si>
-    <t>0.702 +/- 0.031</t>
-  </si>
-  <si>
-    <t>0.698 +/- 0.024</t>
-  </si>
-  <si>
-    <t>32.639 +/- 1.948</t>
-  </si>
-  <si>
-    <t>44.334 +/- 3.237</t>
-  </si>
-  <si>
-    <t>0.487 +/- 0.037</t>
-  </si>
-  <si>
-    <t>0.697 +/- 0.027</t>
-  </si>
-  <si>
-    <t>0.693 +/- 0.021</t>
-  </si>
-  <si>
-    <t>32.182 +/- 1.357</t>
-  </si>
-  <si>
-    <t>43.864 +/- 2.656</t>
-  </si>
-  <si>
-    <t>0.497 +/- 0.041</t>
-  </si>
-  <si>
-    <t>0.704 +/- 0.030</t>
-  </si>
-  <si>
-    <t>0.701 +/- 0.017</t>
-  </si>
-  <si>
-    <t>Clinical_CellType_Module + Pathways</t>
-  </si>
-  <si>
-    <t>32.281 +/- 1.839</t>
-  </si>
-  <si>
-    <t>44.051 +/- 3.463</t>
-  </si>
-  <si>
-    <t>0.491 +/- 0.035</t>
-  </si>
-  <si>
-    <t>0.700 +/- 0.025</t>
-  </si>
-  <si>
-    <t>0.694 +/- 0.015</t>
-  </si>
-  <si>
-    <t>32.263 +/- 0.481</t>
-  </si>
-  <si>
-    <t>43.787 +/- 1.517</t>
-  </si>
-  <si>
-    <t>0.497 +/- 0.021</t>
-  </si>
-  <si>
-    <t>0.705 +/- 0.015</t>
-  </si>
-  <si>
-    <t>0.697 +/- 0.016</t>
-  </si>
-  <si>
-    <t>32.419 +/- 1.452</t>
-  </si>
-  <si>
-    <t>44.066 +/- 2.229</t>
-  </si>
-  <si>
-    <t>0.490 +/- 0.039</t>
-  </si>
-  <si>
-    <t>0.700 +/- 0.027</t>
-  </si>
-  <si>
-    <t>0.695 +/- 0.027</t>
-  </si>
-  <si>
-    <t>Gene Expr + Mutation</t>
-  </si>
-  <si>
-    <t>31.480 +/- 0.982</t>
-  </si>
-  <si>
-    <t>43.085 +/- 1.842</t>
-  </si>
-  <si>
-    <t>0.513 +/- 0.033</t>
-  </si>
-  <si>
-    <t>0.716 +/- 0.023</t>
-  </si>
-  <si>
-    <t>0.710 +/- 0.021</t>
-  </si>
-  <si>
-    <t>31.210 +/- 1.213</t>
-  </si>
-  <si>
-    <t>42.732 +/- 1.990</t>
-  </si>
-  <si>
-    <t>0.521 +/- 0.025</t>
-  </si>
-  <si>
-    <t>0.721 +/- 0.017</t>
-  </si>
-  <si>
-    <t>0.716 +/- 0.020</t>
-  </si>
-  <si>
-    <t>31.535 +/- 1.505</t>
-  </si>
-  <si>
-    <t>43.145 +/- 2.130</t>
-  </si>
-  <si>
-    <t>0.513 +/- 0.030</t>
-  </si>
-  <si>
-    <t>0.716 +/- 0.021</t>
-  </si>
-  <si>
-    <t>0.709 +/- 0.020</t>
-  </si>
-  <si>
-    <t>Gene Expr + Pathways</t>
-  </si>
-  <si>
-    <t>31.483 +/- 0.670</t>
-  </si>
-  <si>
-    <t>43.031 +/- 0.969</t>
-  </si>
-  <si>
-    <t>0.515 +/- 0.014</t>
-  </si>
-  <si>
-    <t>0.718 +/- 0.010</t>
-  </si>
-  <si>
     <t>31.300 +/- 1.906</t>
   </si>
   <si>
@@ -2627,21 +2630,6 @@
   </si>
   <si>
     <t>0.712 +/- 0.012</t>
-  </si>
-  <si>
-    <t>31.054 +/- 0.742</t>
-  </si>
-  <si>
-    <t>42.687 +/- 1.458</t>
-  </si>
-  <si>
-    <t>0.525 +/- 0.021</t>
-  </si>
-  <si>
-    <t>0.724 +/- 0.015</t>
-  </si>
-  <si>
-    <t>0.719 +/- 0.011</t>
   </si>
   <si>
     <t>31.299 +/- 1.219</t>
@@ -2874,14 +2862,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -3114,7 +3102,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3204,6 +3192,9 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -3236,10 +3227,10 @@
     </xf>
     <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3248,7 +3239,7 @@
     <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -3314,23 +3305,23 @@
     <xf borderId="6" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -6756,35 +6747,35 @@
       <c r="D86" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="E86" s="31" t="s">
+      <c r="E86" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="F86" s="31">
-        <v>37.845</v>
-      </c>
-      <c r="G86" s="31" t="s">
+      <c r="F86" s="33">
+        <v>37.712</v>
+      </c>
+      <c r="G86" s="33" t="s">
         <v>373</v>
       </c>
-      <c r="H86" s="31">
-        <v>51.471</v>
-      </c>
-      <c r="I86" s="31" t="s">
+      <c r="H86" s="33">
+        <v>51.342</v>
+      </c>
+      <c r="I86" s="33" t="s">
         <v>374</v>
       </c>
-      <c r="J86" s="31">
-        <v>0.472</v>
-      </c>
-      <c r="K86" s="31" t="s">
+      <c r="J86" s="33">
+        <v>0.475</v>
+      </c>
+      <c r="K86" s="33" t="s">
         <v>375</v>
       </c>
-      <c r="L86" s="31">
-        <v>0.687</v>
-      </c>
-      <c r="M86" s="31" t="s">
+      <c r="L86" s="33">
+        <v>0.69</v>
+      </c>
+      <c r="M86" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="N86" s="31">
-        <v>0.682</v>
+      <c r="N86" s="33">
+        <v>0.685</v>
       </c>
     </row>
     <row r="87">
@@ -6798,34 +6789,34 @@
       <c r="D87" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E87" s="33" t="s">
+      <c r="E87" s="34" t="s">
         <v>377</v>
       </c>
-      <c r="F87" s="33">
+      <c r="F87" s="34">
         <v>37.711</v>
       </c>
-      <c r="G87" s="33" t="s">
+      <c r="G87" s="34" t="s">
         <v>378</v>
       </c>
-      <c r="H87" s="33">
+      <c r="H87" s="34">
         <v>51.26</v>
       </c>
-      <c r="I87" s="33" t="s">
+      <c r="I87" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="J87" s="33">
+      <c r="J87" s="34">
         <v>0.474</v>
       </c>
-      <c r="K87" s="33" t="s">
+      <c r="K87" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="L87" s="33">
+      <c r="L87" s="34">
         <v>0.688</v>
       </c>
-      <c r="M87" s="33" t="s">
+      <c r="M87" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="N87" s="33">
+      <c r="N87" s="34">
         <v>0.684</v>
       </c>
     </row>
@@ -7478,34 +7469,34 @@
       <c r="D105" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E105" s="34" t="s">
+      <c r="E105" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="F105" s="34">
+      <c r="F105" s="35">
         <v>40.52</v>
       </c>
-      <c r="G105" s="34" t="s">
+      <c r="G105" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H105" s="34">
+      <c r="H105" s="35">
         <v>54.87</v>
       </c>
-      <c r="I105" s="34" t="s">
+      <c r="I105" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="J105" s="34">
+      <c r="J105" s="35">
         <v>0.424</v>
       </c>
-      <c r="K105" s="34" t="s">
+      <c r="K105" s="35" t="s">
         <v>461</v>
       </c>
-      <c r="L105" s="34">
+      <c r="L105" s="35">
         <v>0.651</v>
       </c>
-      <c r="M105" s="34" t="s">
+      <c r="M105" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="N105" s="34">
+      <c r="N105" s="35">
         <v>0.643</v>
       </c>
     </row>
@@ -7964,34 +7955,34 @@
       <c r="D118" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E118" s="35" t="s">
+      <c r="E118" s="36" t="s">
         <v>516</v>
       </c>
-      <c r="F118" s="35">
+      <c r="F118" s="36">
         <v>39.532</v>
       </c>
-      <c r="G118" s="35" t="s">
+      <c r="G118" s="36" t="s">
         <v>517</v>
       </c>
-      <c r="H118" s="35">
+      <c r="H118" s="36">
         <v>53.718</v>
       </c>
-      <c r="I118" s="35" t="s">
+      <c r="I118" s="36" t="s">
         <v>518</v>
       </c>
-      <c r="J118" s="35">
+      <c r="J118" s="36">
         <v>0.425</v>
       </c>
-      <c r="K118" s="35" t="s">
+      <c r="K118" s="36" t="s">
         <v>519</v>
       </c>
-      <c r="L118" s="35">
+      <c r="L118" s="36">
         <v>0.652</v>
       </c>
-      <c r="M118" s="35" t="s">
+      <c r="M118" s="36" t="s">
         <v>520</v>
       </c>
-      <c r="N118" s="35">
+      <c r="N118" s="36">
         <v>0.648</v>
       </c>
     </row>
@@ -8323,7 +8314,7 @@
       <c r="E128" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="F128" s="35">
+      <c r="F128" s="36">
         <v>40.332</v>
       </c>
       <c r="G128" s="6" t="s">
@@ -8389,7 +8380,7 @@
       <c r="M129" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="N129" s="35">
+      <c r="N129" s="36">
         <v>0.629</v>
       </c>
     </row>
@@ -8438,31 +8429,31 @@
       <c r="D131" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E131" s="35" t="s">
+      <c r="E131" s="36" t="s">
         <v>576</v>
       </c>
       <c r="F131" s="10">
         <v>40.403</v>
       </c>
-      <c r="G131" s="35" t="s">
+      <c r="G131" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="H131" s="35">
+      <c r="H131" s="36">
         <v>53.518</v>
       </c>
-      <c r="I131" s="35" t="s">
+      <c r="I131" s="36" t="s">
         <v>578</v>
       </c>
-      <c r="J131" s="35">
+      <c r="J131" s="36">
         <v>0.4</v>
       </c>
-      <c r="K131" s="35" t="s">
+      <c r="K131" s="36" t="s">
         <v>579</v>
       </c>
-      <c r="L131" s="35">
+      <c r="L131" s="36">
         <v>0.633</v>
       </c>
-      <c r="M131" s="35" t="s">
+      <c r="M131" s="36" t="s">
         <v>580</v>
       </c>
       <c r="N131" s="10">
@@ -8520,34 +8511,34 @@
       <c r="D134" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E134" s="36" t="s">
+      <c r="E134" s="37" t="s">
         <v>587</v>
       </c>
-      <c r="F134" s="36">
+      <c r="F134" s="37">
         <v>53.306</v>
       </c>
-      <c r="G134" s="36" t="s">
+      <c r="G134" s="37" t="s">
         <v>588</v>
       </c>
-      <c r="H134" s="36">
+      <c r="H134" s="37">
         <v>68.62</v>
       </c>
-      <c r="I134" s="36" t="s">
+      <c r="I134" s="37" t="s">
         <v>589</v>
       </c>
-      <c r="J134" s="36">
+      <c r="J134" s="37">
         <v>0.146</v>
       </c>
-      <c r="K134" s="36" t="s">
+      <c r="K134" s="37" t="s">
         <v>590</v>
       </c>
-      <c r="L134" s="36">
+      <c r="L134" s="37">
         <v>0.382</v>
       </c>
-      <c r="M134" s="36" t="s">
+      <c r="M134" s="37" t="s">
         <v>591</v>
       </c>
-      <c r="N134" s="36">
+      <c r="N134" s="37">
         <v>0.399</v>
       </c>
     </row>
@@ -8555,7 +8546,7 @@
       <c r="A135" s="7"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
-      <c r="D135" s="37" t="s">
+      <c r="D135" s="38" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="6" t="s">
@@ -8603,7 +8594,7 @@
       <c r="E136" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="F136" s="35">
+      <c r="F136" s="36">
         <v>39.672</v>
       </c>
       <c r="G136" s="6" t="s">
@@ -8836,7 +8827,7 @@
       <c r="D142" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E142" s="35" t="s">
+      <c r="E142" s="36" t="s">
         <v>626</v>
       </c>
       <c r="F142" s="6">
@@ -8863,7 +8854,7 @@
       <c r="M142" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="N142" s="35">
+      <c r="N142" s="36">
         <v>0.647</v>
       </c>
     </row>
@@ -8918,25 +8909,25 @@
       <c r="F144" s="10">
         <v>39.936</v>
       </c>
-      <c r="G144" s="35" t="s">
+      <c r="G144" s="36" t="s">
         <v>637</v>
       </c>
-      <c r="H144" s="35">
+      <c r="H144" s="36">
         <v>54.058</v>
       </c>
-      <c r="I144" s="35" t="s">
+      <c r="I144" s="36" t="s">
         <v>638</v>
       </c>
       <c r="J144" s="10">
         <v>0.419</v>
       </c>
-      <c r="K144" s="35" t="s">
+      <c r="K144" s="36" t="s">
         <v>639</v>
       </c>
       <c r="L144" s="10">
         <v>0.647</v>
       </c>
-      <c r="M144" s="35" t="s">
+      <c r="M144" s="36" t="s">
         <v>640</v>
       </c>
       <c r="N144" s="10">
@@ -9072,2492 +9063,2492 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="39" t="s">
         <v>641</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="39" t="s">
         <v>642</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="40" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>348</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>643</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="43" t="s">
         <v>644</v>
       </c>
-      <c r="D2" s="41">
+      <c r="D2" s="42">
         <v>494.0</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="42" t="s">
         <v>645</v>
       </c>
-      <c r="G2" s="41">
+      <c r="G2" s="42">
         <v>38.601</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="42" t="s">
         <v>646</v>
       </c>
-      <c r="I2" s="41">
+      <c r="I2" s="42">
         <v>52.029</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="42" t="s">
         <v>647</v>
       </c>
-      <c r="K2" s="41">
+      <c r="K2" s="42">
         <v>0.45</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="42" t="s">
         <v>648</v>
       </c>
-      <c r="M2" s="41">
+      <c r="M2" s="42">
         <v>0.671</v>
       </c>
-      <c r="N2" s="41" t="s">
+      <c r="N2" s="42" t="s">
         <v>649</v>
       </c>
-      <c r="O2" s="41">
+      <c r="O2" s="42">
         <v>0.663</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="42" t="s">
         <v>650</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="41">
+      <c r="C3" s="44"/>
+      <c r="D3" s="42">
         <v>277.0</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="42" t="s">
         <v>651</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="42">
         <v>38.968</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="42" t="s">
         <v>652</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="42">
         <v>52.458</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="42" t="s">
         <v>653</v>
       </c>
-      <c r="K3" s="41">
+      <c r="K3" s="42">
         <v>0.442</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="42" t="s">
         <v>654</v>
       </c>
-      <c r="M3" s="41">
+      <c r="M3" s="42">
         <v>0.665</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="42" t="s">
         <v>655</v>
       </c>
-      <c r="O3" s="41">
+      <c r="O3" s="42">
         <v>0.658</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43"/>
-      <c r="B4" s="41" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="42" t="s">
         <v>656</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="41">
+      <c r="C4" s="45"/>
+      <c r="D4" s="42">
         <v>750.0</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="42" t="s">
         <v>657</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="42">
         <v>38.912</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="42" t="s">
         <v>658</v>
       </c>
-      <c r="I4" s="41">
+      <c r="I4" s="42">
         <v>52.341</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="42" t="s">
         <v>659</v>
       </c>
-      <c r="K4" s="41">
+      <c r="K4" s="42">
         <v>0.443</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="42" t="s">
         <v>660</v>
       </c>
-      <c r="M4" s="41">
+      <c r="M4" s="42">
         <v>0.666</v>
       </c>
-      <c r="N4" s="41" t="s">
+      <c r="N4" s="42" t="s">
         <v>661</v>
       </c>
-      <c r="O4" s="41">
+      <c r="O4" s="42">
         <v>0.659</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43"/>
-      <c r="B5" s="45" t="s">
+      <c r="A5" s="44"/>
+      <c r="B5" s="46" t="s">
         <v>643</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="43" t="s">
         <v>662</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="42">
         <v>1266.0</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="42" t="s">
         <v>663</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="42">
         <v>38.005</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="42" t="s">
         <v>664</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="42">
         <v>51.568</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="42" t="s">
         <v>665</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="42">
         <v>0.469</v>
       </c>
-      <c r="L5" s="41" t="s">
+      <c r="L5" s="42" t="s">
         <v>666</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="42">
         <v>0.685</v>
       </c>
-      <c r="N5" s="41" t="s">
+      <c r="N5" s="42" t="s">
         <v>667</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="42">
         <v>0.68</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43"/>
-      <c r="B6" s="46" t="s">
+      <c r="A6" s="44"/>
+      <c r="B6" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="41">
+      <c r="C6" s="44"/>
+      <c r="D6" s="42">
         <v>1049.0</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="42" t="s">
         <v>668</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="42">
         <v>38.051</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="42" t="s">
         <v>669</v>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="42">
         <v>51.82</v>
       </c>
-      <c r="J6" s="41" t="s">
+      <c r="J6" s="42" t="s">
         <v>670</v>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="42">
         <v>0.466</v>
       </c>
-      <c r="L6" s="41" t="s">
+      <c r="L6" s="42" t="s">
         <v>671</v>
       </c>
-      <c r="M6" s="41">
+      <c r="M6" s="42">
         <v>0.682</v>
       </c>
-      <c r="N6" s="41" t="s">
+      <c r="N6" s="42" t="s">
         <v>672</v>
       </c>
-      <c r="O6" s="41">
+      <c r="O6" s="42">
         <v>0.677</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43"/>
-      <c r="B7" s="46" t="s">
+      <c r="A7" s="44"/>
+      <c r="B7" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="41">
+      <c r="C7" s="45"/>
+      <c r="D7" s="42">
         <v>1522.0</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="42" t="s">
         <v>673</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="42">
         <v>38.216</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="42" t="s">
         <v>674</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="42">
         <v>51.501</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="42" t="s">
         <v>675</v>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="42">
         <v>0.467</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="42" t="s">
         <v>676</v>
       </c>
-      <c r="M7" s="41">
+      <c r="M7" s="42">
         <v>0.683</v>
       </c>
-      <c r="N7" s="41" t="s">
+      <c r="N7" s="42" t="s">
         <v>677</v>
       </c>
-      <c r="O7" s="41">
+      <c r="O7" s="42">
         <v>0.678</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43"/>
-      <c r="B8" s="45" t="s">
+      <c r="A8" s="44"/>
+      <c r="B8" s="46" t="s">
         <v>643</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="43" t="s">
         <v>678</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="42">
         <v>856.0</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="42" t="s">
         <v>679</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="42">
         <v>39.996</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="42" t="s">
         <v>680</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="42">
         <v>53.631</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="42" t="s">
         <v>681</v>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="42">
         <v>0.42</v>
       </c>
-      <c r="L8" s="41" t="s">
+      <c r="L8" s="42" t="s">
         <v>682</v>
       </c>
-      <c r="M8" s="41">
+      <c r="M8" s="42">
         <v>0.648</v>
       </c>
-      <c r="N8" s="41" t="s">
+      <c r="N8" s="42" t="s">
         <v>683</v>
       </c>
-      <c r="O8" s="41">
+      <c r="O8" s="42">
         <v>0.646</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43"/>
-      <c r="B9" s="46" t="s">
+      <c r="A9" s="44"/>
+      <c r="B9" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="41">
+      <c r="C9" s="44"/>
+      <c r="D9" s="42">
         <v>639.0</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="42" t="s">
         <v>684</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="42">
         <v>40.147</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="42" t="s">
         <v>685</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="42">
         <v>53.896</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="42" t="s">
         <v>686</v>
       </c>
-      <c r="K9" s="41">
+      <c r="K9" s="42">
         <v>0.418</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="42" t="s">
         <v>687</v>
       </c>
-      <c r="M9" s="41">
+      <c r="M9" s="42">
         <v>0.647</v>
       </c>
-      <c r="N9" s="41" t="s">
+      <c r="N9" s="42" t="s">
         <v>688</v>
       </c>
-      <c r="O9" s="41">
+      <c r="O9" s="42">
         <v>0.646</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43"/>
-      <c r="B10" s="46" t="s">
+      <c r="A10" s="44"/>
+      <c r="B10" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="41">
+      <c r="C10" s="45"/>
+      <c r="D10" s="42">
         <v>1112.0</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="42" t="s">
         <v>689</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="42">
         <v>40.08</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="42" t="s">
         <v>690</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="42">
         <v>53.805</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="J10" s="42" t="s">
         <v>691</v>
       </c>
-      <c r="K10" s="41">
+      <c r="K10" s="42">
         <v>0.415</v>
       </c>
-      <c r="L10" s="41" t="s">
+      <c r="L10" s="42" t="s">
         <v>692</v>
       </c>
-      <c r="M10" s="41">
+      <c r="M10" s="42">
         <v>0.644</v>
       </c>
-      <c r="N10" s="41" t="s">
+      <c r="N10" s="42" t="s">
         <v>693</v>
       </c>
-      <c r="O10" s="41">
+      <c r="O10" s="42">
         <v>0.643</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43"/>
-      <c r="B11" s="45" t="s">
+      <c r="A11" s="44"/>
+      <c r="B11" s="46" t="s">
         <v>643</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="43" t="s">
         <v>694</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="42">
         <v>581.0</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="42" t="s">
         <v>695</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="42">
         <v>39.043</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="42" t="s">
         <v>696</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="42">
         <v>52.426</v>
       </c>
-      <c r="J11" s="41" t="s">
+      <c r="J11" s="42" t="s">
         <v>697</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="42">
         <v>0.445</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="42" t="s">
         <v>698</v>
       </c>
-      <c r="M11" s="41">
+      <c r="M11" s="42">
         <v>0.667</v>
       </c>
-      <c r="N11" s="41" t="s">
+      <c r="N11" s="42" t="s">
         <v>699</v>
       </c>
-      <c r="O11" s="41">
+      <c r="O11" s="42">
         <v>0.659</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="44"/>
+      <c r="B12" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="41">
+      <c r="C12" s="44"/>
+      <c r="D12" s="42">
         <v>364.0</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="42" t="s">
         <v>700</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="42">
         <v>39.022</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="42" t="s">
         <v>701</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="42">
         <v>52.378</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="J12" s="42" t="s">
         <v>702</v>
       </c>
-      <c r="K12" s="41">
+      <c r="K12" s="42">
         <v>0.443</v>
       </c>
-      <c r="L12" s="41" t="s">
+      <c r="L12" s="42" t="s">
         <v>703</v>
       </c>
-      <c r="M12" s="41">
+      <c r="M12" s="42">
         <v>0.666</v>
       </c>
-      <c r="N12" s="41" t="s">
+      <c r="N12" s="42" t="s">
         <v>704</v>
       </c>
-      <c r="O12" s="41">
+      <c r="O12" s="42">
         <v>0.657</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43"/>
-      <c r="B13" s="46" t="s">
+      <c r="A13" s="44"/>
+      <c r="B13" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="41">
+      <c r="C13" s="45"/>
+      <c r="D13" s="42">
         <v>837.0</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="42" t="s">
         <v>705</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="42">
         <v>39.189</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="42" t="s">
         <v>706</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="42">
         <v>52.407</v>
       </c>
-      <c r="J13" s="41" t="s">
+      <c r="J13" s="42" t="s">
         <v>707</v>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="42">
         <v>0.441</v>
       </c>
-      <c r="L13" s="41" t="s">
+      <c r="L13" s="42" t="s">
         <v>708</v>
       </c>
-      <c r="M13" s="41">
+      <c r="M13" s="42">
         <v>0.664</v>
       </c>
-      <c r="N13" s="41" t="s">
+      <c r="N13" s="42" t="s">
         <v>709</v>
       </c>
-      <c r="O13" s="41">
+      <c r="O13" s="42">
         <v>0.656</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43"/>
-      <c r="B14" s="41" t="s">
+      <c r="A14" s="44"/>
+      <c r="B14" s="42" t="s">
         <v>643</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="43" t="s">
         <v>710</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="42">
         <v>1287.0</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="42" t="s">
         <v>711</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="42">
         <v>38.137</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="42" t="s">
         <v>712</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="42">
         <v>51.811</v>
       </c>
-      <c r="J14" s="41" t="s">
+      <c r="J14" s="42" t="s">
         <v>713</v>
       </c>
-      <c r="K14" s="41">
+      <c r="K14" s="42">
         <v>0.465</v>
       </c>
-      <c r="L14" s="41" t="s">
+      <c r="L14" s="42" t="s">
         <v>714</v>
       </c>
-      <c r="M14" s="41">
+      <c r="M14" s="42">
         <v>0.682</v>
       </c>
-      <c r="N14" s="41" t="s">
+      <c r="N14" s="42" t="s">
         <v>715</v>
       </c>
-      <c r="O14" s="41">
+      <c r="O14" s="42">
         <v>0.676</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43"/>
-      <c r="B15" s="41" t="s">
+      <c r="A15" s="44"/>
+      <c r="B15" s="42" t="s">
         <v>650</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="41">
+      <c r="C15" s="44"/>
+      <c r="D15" s="42">
         <v>1070.0</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="42" t="s">
         <v>716</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="42">
         <v>37.808</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="42" t="s">
         <v>717</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="42">
         <v>51.586</v>
       </c>
-      <c r="J15" s="41" t="s">
+      <c r="J15" s="42" t="s">
         <v>718</v>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="42">
         <v>0.471</v>
       </c>
-      <c r="L15" s="41" t="s">
+      <c r="L15" s="42" t="s">
         <v>719</v>
       </c>
-      <c r="M15" s="41">
+      <c r="M15" s="42">
         <v>0.686</v>
       </c>
-      <c r="N15" s="41" t="s">
+      <c r="N15" s="42" t="s">
         <v>720</v>
       </c>
-      <c r="O15" s="41">
+      <c r="O15" s="42">
         <v>0.681</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43"/>
-      <c r="B16" s="41" t="s">
+      <c r="A16" s="44"/>
+      <c r="B16" s="42" t="s">
         <v>656</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="41">
+      <c r="C16" s="45"/>
+      <c r="D16" s="42">
         <v>1543.0</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="42" t="s">
         <v>721</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="42">
         <v>37.875</v>
       </c>
-      <c r="H16" s="41" t="s">
+      <c r="H16" s="42" t="s">
         <v>722</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="42">
         <v>51.506</v>
       </c>
-      <c r="J16" s="41" t="s">
+      <c r="J16" s="42" t="s">
         <v>723</v>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="42">
         <v>0.47</v>
       </c>
-      <c r="L16" s="41" t="s">
+      <c r="L16" s="42" t="s">
         <v>724</v>
       </c>
-      <c r="M16" s="41">
+      <c r="M16" s="42">
         <v>0.686</v>
       </c>
-      <c r="N16" s="41" t="s">
+      <c r="N16" s="42" t="s">
         <v>725</v>
       </c>
-      <c r="O16" s="41">
+      <c r="O16" s="42">
         <v>0.681</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43"/>
-      <c r="B17" s="41" t="s">
+      <c r="A17" s="44"/>
+      <c r="B17" s="42" t="s">
         <v>643</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="43" t="s">
         <v>726</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <v>877.0</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="42" t="s">
         <v>727</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="42">
         <v>37.787</v>
       </c>
-      <c r="H17" s="41" t="s">
+      <c r="H17" s="42" t="s">
         <v>728</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="42">
         <v>50.949</v>
       </c>
-      <c r="J17" s="41" t="s">
+      <c r="J17" s="42" t="s">
         <v>729</v>
       </c>
-      <c r="K17" s="41">
+      <c r="K17" s="42">
         <v>0.469</v>
       </c>
-      <c r="L17" s="41" t="s">
+      <c r="L17" s="42" t="s">
         <v>730</v>
       </c>
-      <c r="M17" s="41">
+      <c r="M17" s="42">
         <v>0.685</v>
       </c>
-      <c r="N17" s="41" t="s">
+      <c r="N17" s="42" t="s">
         <v>731</v>
       </c>
-      <c r="O17" s="41">
+      <c r="O17" s="42">
         <v>0.681</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43"/>
-      <c r="B18" s="38" t="s">
+      <c r="A18" s="44"/>
+      <c r="B18" s="39" t="s">
         <v>650</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="38">
+      <c r="C18" s="44"/>
+      <c r="D18" s="39">
         <v>660.0</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="39" t="s">
         <v>732</v>
       </c>
-      <c r="G18" s="38">
+      <c r="G18" s="39">
         <v>37.557</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="39" t="s">
         <v>733</v>
       </c>
-      <c r="I18" s="38">
+      <c r="I18" s="39">
         <v>51.061</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="39" t="s">
         <v>734</v>
       </c>
-      <c r="K18" s="38">
+      <c r="K18" s="39">
         <v>0.475</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="39" t="s">
         <v>735</v>
       </c>
-      <c r="M18" s="38">
+      <c r="M18" s="39">
         <v>0.689</v>
       </c>
-      <c r="N18" s="38" t="s">
+      <c r="N18" s="39" t="s">
         <v>736</v>
       </c>
-      <c r="O18" s="38">
+      <c r="O18" s="39">
         <v>0.685</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43"/>
-      <c r="B19" s="41" t="s">
+      <c r="A19" s="44"/>
+      <c r="B19" s="42" t="s">
         <v>656</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="41">
+      <c r="C19" s="45"/>
+      <c r="D19" s="42">
         <v>1133.0</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="42" t="s">
         <v>737</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="42">
         <v>38.096</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="H19" s="42" t="s">
         <v>738</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="42">
         <v>51.365</v>
       </c>
-      <c r="J19" s="41" t="s">
+      <c r="J19" s="42" t="s">
         <v>739</v>
       </c>
-      <c r="K19" s="41">
+      <c r="K19" s="42">
         <v>0.465</v>
       </c>
-      <c r="L19" s="41" t="s">
+      <c r="L19" s="42" t="s">
         <v>740</v>
       </c>
-      <c r="M19" s="41">
+      <c r="M19" s="42">
         <v>0.682</v>
       </c>
-      <c r="N19" s="41" t="s">
+      <c r="N19" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="O19" s="41">
+      <c r="O19" s="42">
         <v>0.677</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43"/>
-      <c r="B20" s="41" t="s">
+      <c r="A20" s="44"/>
+      <c r="B20" s="42" t="s">
         <v>643</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="43" t="s">
         <v>742</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="42">
         <v>602.0</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="42" t="s">
         <v>743</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="42">
         <v>38.306</v>
       </c>
-      <c r="H20" s="41" t="s">
+      <c r="H20" s="42" t="s">
         <v>744</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="42">
         <v>51.572</v>
       </c>
-      <c r="J20" s="41" t="s">
+      <c r="J20" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="K20" s="41">
+      <c r="K20" s="42">
         <v>0.458</v>
       </c>
-      <c r="L20" s="41" t="s">
+      <c r="L20" s="42" t="s">
         <v>746</v>
       </c>
-      <c r="M20" s="41">
+      <c r="M20" s="42">
         <v>0.677</v>
       </c>
-      <c r="N20" s="41" t="s">
+      <c r="N20" s="42" t="s">
         <v>747</v>
       </c>
-      <c r="O20" s="41">
+      <c r="O20" s="42">
         <v>0.67</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43"/>
-      <c r="B21" s="41" t="s">
+      <c r="A21" s="44"/>
+      <c r="B21" s="42" t="s">
         <v>650</v>
       </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="41">
+      <c r="C21" s="44"/>
+      <c r="D21" s="42">
         <v>385.0</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="42" t="s">
         <v>748</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="42">
         <v>38.593</v>
       </c>
-      <c r="H21" s="41" t="s">
+      <c r="H21" s="42" t="s">
         <v>749</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="42">
         <v>52.185</v>
       </c>
-      <c r="J21" s="41" t="s">
+      <c r="J21" s="42" t="s">
         <v>750</v>
       </c>
-      <c r="K21" s="41">
+      <c r="K21" s="42">
         <v>0.451</v>
       </c>
-      <c r="L21" s="41" t="s">
+      <c r="L21" s="42" t="s">
         <v>751</v>
       </c>
-      <c r="M21" s="41">
+      <c r="M21" s="42">
         <v>0.672</v>
       </c>
-      <c r="N21" s="41" t="s">
+      <c r="N21" s="42" t="s">
         <v>752</v>
       </c>
-      <c r="O21" s="41">
+      <c r="O21" s="42">
         <v>0.664</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43"/>
-      <c r="B22" s="41" t="s">
+      <c r="A22" s="44"/>
+      <c r="B22" s="42" t="s">
         <v>656</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="41">
+      <c r="C22" s="45"/>
+      <c r="D22" s="42">
         <v>858.0</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="42" t="s">
         <v>753</v>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="42">
         <v>38.429</v>
       </c>
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="42" t="s">
         <v>754</v>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="42">
         <v>51.723</v>
       </c>
-      <c r="J22" s="41" t="s">
+      <c r="J22" s="42" t="s">
         <v>755</v>
       </c>
-      <c r="K22" s="41">
+      <c r="K22" s="42">
         <v>0.458</v>
       </c>
-      <c r="L22" s="41" t="s">
+      <c r="L22" s="42" t="s">
         <v>756</v>
       </c>
-      <c r="M22" s="41">
+      <c r="M22" s="42">
         <v>0.677</v>
       </c>
-      <c r="N22" s="41" t="s">
+      <c r="N22" s="42" t="s">
         <v>757</v>
       </c>
-      <c r="O22" s="41">
+      <c r="O22" s="42">
         <v>0.668</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43"/>
-      <c r="B23" s="41" t="s">
+      <c r="A23" s="44"/>
+      <c r="B23" s="42" t="s">
         <v>643</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="43" t="s">
         <v>758</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="42">
         <v>1649.0</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="42" t="s">
         <v>759</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="42">
         <v>37.946</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="42" t="s">
         <v>760</v>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="42">
         <v>51.612</v>
       </c>
-      <c r="J23" s="41" t="s">
+      <c r="J23" s="42" t="s">
         <v>761</v>
       </c>
-      <c r="K23" s="41">
+      <c r="K23" s="42">
         <v>0.47</v>
       </c>
-      <c r="L23" s="41" t="s">
+      <c r="L23" s="42" t="s">
         <v>762</v>
       </c>
-      <c r="M23" s="41">
+      <c r="M23" s="42">
         <v>0.685</v>
       </c>
-      <c r="N23" s="41" t="s">
+      <c r="N23" s="42" t="s">
         <v>763</v>
       </c>
-      <c r="O23" s="41">
+      <c r="O23" s="42">
         <v>0.68</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43"/>
-      <c r="B24" s="41" t="s">
+      <c r="A24" s="44"/>
+      <c r="B24" s="42" t="s">
         <v>650</v>
       </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="41">
+      <c r="C24" s="44"/>
+      <c r="D24" s="42">
         <v>1432.0</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="42" t="s">
         <v>764</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="42">
         <v>37.904</v>
       </c>
-      <c r="H24" s="41" t="s">
+      <c r="H24" s="42" t="s">
         <v>765</v>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="42">
         <v>51.558</v>
       </c>
-      <c r="J24" s="41" t="s">
+      <c r="J24" s="42" t="s">
         <v>766</v>
       </c>
-      <c r="K24" s="41">
+      <c r="K24" s="42">
         <v>0.469</v>
       </c>
-      <c r="L24" s="41" t="s">
+      <c r="L24" s="42" t="s">
         <v>767</v>
       </c>
-      <c r="M24" s="41">
+      <c r="M24" s="42">
         <v>0.685</v>
       </c>
-      <c r="N24" s="41" t="s">
+      <c r="N24" s="42" t="s">
         <v>768</v>
       </c>
-      <c r="O24" s="41">
+      <c r="O24" s="42">
         <v>0.68</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="41" t="s">
+      <c r="A25" s="44"/>
+      <c r="B25" s="42" t="s">
         <v>656</v>
       </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="41">
+      <c r="C25" s="45"/>
+      <c r="D25" s="42">
         <v>1905.0</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="F25" s="42" t="s">
         <v>769</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="42">
         <v>37.888</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="H25" s="42" t="s">
         <v>770</v>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="42">
         <v>51.537</v>
       </c>
-      <c r="J25" s="41" t="s">
+      <c r="J25" s="42" t="s">
         <v>771</v>
       </c>
-      <c r="K25" s="41">
+      <c r="K25" s="42">
         <v>0.47</v>
       </c>
-      <c r="L25" s="41" t="s">
+      <c r="L25" s="42" t="s">
         <v>772</v>
       </c>
-      <c r="M25" s="41">
+      <c r="M25" s="42">
         <v>0.686</v>
       </c>
-      <c r="N25" s="41" t="s">
+      <c r="N25" s="42" t="s">
         <v>773</v>
       </c>
-      <c r="O25" s="41">
+      <c r="O25" s="42">
         <v>0.681</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43"/>
-      <c r="B26" s="41" t="s">
+      <c r="A26" s="44"/>
+      <c r="B26" s="42" t="s">
         <v>643</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="43" t="s">
         <v>774</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="42">
         <v>1374.0</v>
       </c>
-      <c r="E26" s="41" t="s">
+      <c r="E26" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="41" t="s">
+      <c r="F26" s="42" t="s">
         <v>775</v>
       </c>
-      <c r="G26" s="41">
+      <c r="G26" s="42">
         <v>38.375</v>
       </c>
-      <c r="H26" s="41" t="s">
+      <c r="H26" s="42" t="s">
         <v>776</v>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="42">
         <v>52.08</v>
       </c>
-      <c r="J26" s="41" t="s">
+      <c r="J26" s="42" t="s">
         <v>777</v>
       </c>
-      <c r="K26" s="41">
+      <c r="K26" s="42">
         <v>0.458</v>
       </c>
-      <c r="L26" s="41" t="s">
+      <c r="L26" s="42" t="s">
         <v>778</v>
       </c>
-      <c r="M26" s="41">
+      <c r="M26" s="42">
         <v>0.676</v>
       </c>
-      <c r="N26" s="41" t="s">
+      <c r="N26" s="42" t="s">
+        <v>779</v>
+      </c>
+      <c r="O26" s="42">
+        <v>0.669</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44"/>
+      <c r="B27" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="C27" s="44"/>
+      <c r="D27" s="42">
+        <v>1157.0</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>780</v>
+      </c>
+      <c r="G27" s="42">
+        <v>37.978</v>
+      </c>
+      <c r="H27" s="42" t="s">
+        <v>781</v>
+      </c>
+      <c r="I27" s="42">
+        <v>51.835</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>782</v>
+      </c>
+      <c r="K27" s="42">
+        <v>0.468</v>
+      </c>
+      <c r="L27" s="42" t="s">
+        <v>783</v>
+      </c>
+      <c r="M27" s="42">
+        <v>0.684</v>
+      </c>
+      <c r="N27" s="42" t="s">
+        <v>784</v>
+      </c>
+      <c r="O27" s="42">
+        <v>0.679</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44"/>
+      <c r="B28" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="42">
+        <v>1630.0</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>785</v>
+      </c>
+      <c r="G28" s="42">
+        <v>38.252</v>
+      </c>
+      <c r="H28" s="42" t="s">
+        <v>786</v>
+      </c>
+      <c r="I28" s="42">
+        <v>51.816</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>787</v>
+      </c>
+      <c r="K28" s="42">
+        <v>0.461</v>
+      </c>
+      <c r="L28" s="42" t="s">
+        <v>788</v>
+      </c>
+      <c r="M28" s="42">
+        <v>0.679</v>
+      </c>
+      <c r="N28" s="42" t="s">
+        <v>789</v>
+      </c>
+      <c r="O28" s="42">
+        <v>0.672</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44"/>
+      <c r="B29" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>790</v>
+      </c>
+      <c r="D29" s="42">
+        <v>964.0</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>791</v>
+      </c>
+      <c r="G29" s="42">
+        <v>38.57</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>792</v>
+      </c>
+      <c r="I29" s="42">
+        <v>51.989</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>793</v>
+      </c>
+      <c r="K29" s="42">
+        <v>0.454</v>
+      </c>
+      <c r="L29" s="42" t="s">
+        <v>794</v>
+      </c>
+      <c r="M29" s="42">
+        <v>0.674</v>
+      </c>
+      <c r="N29" s="42" t="s">
+        <v>795</v>
+      </c>
+      <c r="O29" s="42">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44"/>
+      <c r="B30" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="C30" s="44"/>
+      <c r="D30" s="42">
+        <v>747.0</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>796</v>
+      </c>
+      <c r="G30" s="42">
+        <v>38.423</v>
+      </c>
+      <c r="H30" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="I30" s="42">
+        <v>51.579</v>
+      </c>
+      <c r="J30" s="42" t="s">
+        <v>798</v>
+      </c>
+      <c r="K30" s="42">
+        <v>0.46</v>
+      </c>
+      <c r="L30" s="42" t="s">
+        <v>741</v>
+      </c>
+      <c r="M30" s="42">
+        <v>0.678</v>
+      </c>
+      <c r="N30" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="O30" s="42">
+        <v>0.672</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44"/>
+      <c r="B31" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="C31" s="45"/>
+      <c r="D31" s="42">
+        <v>1220.0</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="G31" s="42">
+        <v>38.622</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>800</v>
+      </c>
+      <c r="I31" s="42">
+        <v>51.711</v>
+      </c>
+      <c r="J31" s="42" t="s">
+        <v>801</v>
+      </c>
+      <c r="K31" s="42">
+        <v>0.46</v>
+      </c>
+      <c r="L31" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="M31" s="42">
+        <v>0.678</v>
+      </c>
+      <c r="N31" s="42" t="s">
+        <v>803</v>
+      </c>
+      <c r="O31" s="42">
+        <v>0.672</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44"/>
+      <c r="B32" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>804</v>
+      </c>
+      <c r="D32" s="42">
+        <v>1670.0</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="48" t="s">
+        <v>805</v>
+      </c>
+      <c r="G32" s="42">
+        <v>38.271</v>
+      </c>
+      <c r="H32" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="I32" s="42">
+        <v>51.62</v>
+      </c>
+      <c r="J32" s="48" t="s">
+        <v>807</v>
+      </c>
+      <c r="K32" s="42">
+        <v>0.466</v>
+      </c>
+      <c r="L32" s="48" t="s">
+        <v>808</v>
+      </c>
+      <c r="M32" s="42">
+        <v>0.683</v>
+      </c>
+      <c r="N32" s="48" t="s">
+        <v>809</v>
+      </c>
+      <c r="O32" s="42">
+        <v>0.678</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44"/>
+      <c r="B33" s="39" t="s">
+        <v>650</v>
+      </c>
+      <c r="C33" s="44"/>
+      <c r="D33" s="39">
+        <v>1453.0</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>810</v>
+      </c>
+      <c r="G33" s="39">
+        <v>37.672</v>
+      </c>
+      <c r="H33" s="39" t="s">
+        <v>811</v>
+      </c>
+      <c r="I33" s="39">
+        <v>51.357</v>
+      </c>
+      <c r="J33" s="39" t="s">
+        <v>812</v>
+      </c>
+      <c r="K33" s="39">
+        <v>0.475</v>
+      </c>
+      <c r="L33" s="39" t="s">
+        <v>813</v>
+      </c>
+      <c r="M33" s="39">
+        <v>0.689</v>
+      </c>
+      <c r="N33" s="39" t="s">
+        <v>814</v>
+      </c>
+      <c r="O33" s="39">
+        <v>0.684</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44"/>
+      <c r="B34" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="C34" s="45"/>
+      <c r="D34" s="42">
+        <v>1926.0</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>815</v>
+      </c>
+      <c r="G34" s="42">
+        <v>38.077</v>
+      </c>
+      <c r="H34" s="42" t="s">
+        <v>816</v>
+      </c>
+      <c r="I34" s="42">
+        <v>51.831</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>817</v>
+      </c>
+      <c r="K34" s="42">
+        <v>0.464</v>
+      </c>
+      <c r="L34" s="42" t="s">
+        <v>818</v>
+      </c>
+      <c r="M34" s="42">
+        <v>0.681</v>
+      </c>
+      <c r="N34" s="42" t="s">
+        <v>819</v>
+      </c>
+      <c r="O34" s="42">
+        <v>0.676</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44"/>
+      <c r="B35" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>820</v>
+      </c>
+      <c r="D35" s="42">
+        <v>1395.0</v>
+      </c>
+      <c r="E35" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>821</v>
+      </c>
+      <c r="G35" s="42">
+        <v>38.022</v>
+      </c>
+      <c r="H35" s="42" t="s">
+        <v>822</v>
+      </c>
+      <c r="I35" s="42">
+        <v>51.66</v>
+      </c>
+      <c r="J35" s="42" t="s">
+        <v>823</v>
+      </c>
+      <c r="K35" s="42">
+        <v>0.467</v>
+      </c>
+      <c r="L35" s="42" t="s">
+        <v>824</v>
+      </c>
+      <c r="M35" s="42">
+        <v>0.683</v>
+      </c>
+      <c r="N35" s="42" t="s">
+        <v>825</v>
+      </c>
+      <c r="O35" s="42">
+        <v>0.677</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44"/>
+      <c r="B36" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="C36" s="44"/>
+      <c r="D36" s="42">
+        <v>1178.0</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>826</v>
+      </c>
+      <c r="G36" s="42">
+        <v>38.011</v>
+      </c>
+      <c r="H36" s="42" t="s">
+        <v>827</v>
+      </c>
+      <c r="I36" s="42">
+        <v>51.852</v>
+      </c>
+      <c r="J36" s="42" t="s">
+        <v>828</v>
+      </c>
+      <c r="K36" s="42">
+        <v>0.469</v>
+      </c>
+      <c r="L36" s="42" t="s">
+        <v>829</v>
+      </c>
+      <c r="M36" s="42">
+        <v>0.685</v>
+      </c>
+      <c r="N36" s="42" t="s">
+        <v>830</v>
+      </c>
+      <c r="O36" s="42">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="44"/>
+      <c r="B37" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="C37" s="45"/>
+      <c r="D37" s="42">
+        <v>1651.0</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>831</v>
+      </c>
+      <c r="G37" s="42">
+        <v>38.128</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>832</v>
+      </c>
+      <c r="I37" s="42">
+        <v>51.767</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>833</v>
+      </c>
+      <c r="K37" s="42">
+        <v>0.463</v>
+      </c>
+      <c r="L37" s="42" t="s">
+        <v>834</v>
+      </c>
+      <c r="M37" s="42">
+        <v>0.681</v>
+      </c>
+      <c r="N37" s="42" t="s">
+        <v>725</v>
+      </c>
+      <c r="O37" s="42">
+        <v>0.676</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="44"/>
+      <c r="B38" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>835</v>
+      </c>
+      <c r="D38" s="42">
+        <v>985.0</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>836</v>
+      </c>
+      <c r="G38" s="42">
+        <v>37.901</v>
+      </c>
+      <c r="H38" s="42" t="s">
+        <v>837</v>
+      </c>
+      <c r="I38" s="42">
+        <v>51.013</v>
+      </c>
+      <c r="J38" s="42" t="s">
+        <v>838</v>
+      </c>
+      <c r="K38" s="42">
+        <v>0.472</v>
+      </c>
+      <c r="L38" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="M38" s="42">
+        <v>0.687</v>
+      </c>
+      <c r="N38" s="42" t="s">
+        <v>840</v>
+      </c>
+      <c r="O38" s="42">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="44"/>
+      <c r="B39" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="C39" s="44"/>
+      <c r="D39" s="42">
+        <v>768.0</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>841</v>
+      </c>
+      <c r="G39" s="42">
+        <v>37.655</v>
+      </c>
+      <c r="H39" s="42" t="s">
+        <v>842</v>
+      </c>
+      <c r="I39" s="42">
+        <v>50.954</v>
+      </c>
+      <c r="J39" s="42" t="s">
+        <v>843</v>
+      </c>
+      <c r="K39" s="42">
+        <v>0.473</v>
+      </c>
+      <c r="L39" s="42" t="s">
+        <v>844</v>
+      </c>
+      <c r="M39" s="42">
+        <v>0.688</v>
+      </c>
+      <c r="N39" s="42" t="s">
+        <v>845</v>
+      </c>
+      <c r="O39" s="42">
+        <v>0.682</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44"/>
+      <c r="B40" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="C40" s="45"/>
+      <c r="D40" s="42">
+        <v>1241.0</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>846</v>
+      </c>
+      <c r="G40" s="42">
+        <v>37.913</v>
+      </c>
+      <c r="H40" s="42" t="s">
+        <v>847</v>
+      </c>
+      <c r="I40" s="42">
+        <v>51.288</v>
+      </c>
+      <c r="J40" s="42" t="s">
+        <v>848</v>
+      </c>
+      <c r="K40" s="42">
+        <v>0.466</v>
+      </c>
+      <c r="L40" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="M40" s="42">
+        <v>0.682</v>
+      </c>
+      <c r="N40" s="42" t="s">
+        <v>849</v>
+      </c>
+      <c r="O40" s="42">
+        <v>0.676</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="44"/>
+      <c r="B41" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>850</v>
+      </c>
+      <c r="D41" s="42">
+        <v>1757.0</v>
+      </c>
+      <c r="E41" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>851</v>
+      </c>
+      <c r="G41" s="42">
+        <v>37.78</v>
+      </c>
+      <c r="H41" s="42" t="s">
+        <v>852</v>
+      </c>
+      <c r="I41" s="42">
+        <v>51.35</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>853</v>
+      </c>
+      <c r="K41" s="42">
+        <v>0.471</v>
+      </c>
+      <c r="L41" s="42" t="s">
+        <v>854</v>
+      </c>
+      <c r="M41" s="42">
+        <v>0.686</v>
+      </c>
+      <c r="N41" s="42" t="s">
+        <v>855</v>
+      </c>
+      <c r="O41" s="42">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="44"/>
+      <c r="B42" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="C42" s="44"/>
+      <c r="D42" s="42">
+        <v>1540.0</v>
+      </c>
+      <c r="E42" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>856</v>
+      </c>
+      <c r="G42" s="42">
+        <v>37.897</v>
+      </c>
+      <c r="H42" s="42" t="s">
+        <v>857</v>
+      </c>
+      <c r="I42" s="42">
+        <v>51.491</v>
+      </c>
+      <c r="J42" s="42" t="s">
+        <v>858</v>
+      </c>
+      <c r="K42" s="42">
+        <v>0.472</v>
+      </c>
+      <c r="L42" s="42" t="s">
+        <v>859</v>
+      </c>
+      <c r="M42" s="42">
+        <v>0.687</v>
+      </c>
+      <c r="N42" s="42" t="s">
+        <v>860</v>
+      </c>
+      <c r="O42" s="42">
+        <v>0.683</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="44"/>
+      <c r="B43" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="42">
+        <v>2013.0</v>
+      </c>
+      <c r="E43" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>861</v>
+      </c>
+      <c r="G43" s="42">
+        <v>37.936</v>
+      </c>
+      <c r="H43" s="42" t="s">
+        <v>862</v>
+      </c>
+      <c r="I43" s="42">
+        <v>51.388</v>
+      </c>
+      <c r="J43" s="42" t="s">
+        <v>863</v>
+      </c>
+      <c r="K43" s="42">
+        <v>0.472</v>
+      </c>
+      <c r="L43" s="42" t="s">
+        <v>864</v>
+      </c>
+      <c r="M43" s="42">
+        <v>0.687</v>
+      </c>
+      <c r="N43" s="42" t="s">
+        <v>865</v>
+      </c>
+      <c r="O43" s="42">
+        <v>0.683</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="44"/>
+      <c r="B44" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>866</v>
+      </c>
+      <c r="D44" s="42">
+        <v>1778.0</v>
+      </c>
+      <c r="E44" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="49" t="s">
+        <v>867</v>
+      </c>
+      <c r="G44" s="49">
+        <v>38.118</v>
+      </c>
+      <c r="H44" s="49" t="s">
+        <v>868</v>
+      </c>
+      <c r="I44" s="49">
+        <v>51.612</v>
+      </c>
+      <c r="J44" s="49" t="s">
+        <v>869</v>
+      </c>
+      <c r="K44" s="49">
+        <v>0.466</v>
+      </c>
+      <c r="L44" s="49" t="s">
+        <v>870</v>
+      </c>
+      <c r="M44" s="49">
+        <v>0.683</v>
+      </c>
+      <c r="N44" s="49" t="s">
+        <v>871</v>
+      </c>
+      <c r="O44" s="49">
+        <v>0.676</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="44"/>
+      <c r="B45" s="39" t="s">
+        <v>650</v>
+      </c>
+      <c r="C45" s="44"/>
+      <c r="D45" s="42">
+        <v>1561.0</v>
+      </c>
+      <c r="E45" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="G45" s="50">
+        <v>37.712</v>
+      </c>
+      <c r="H45" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="I45" s="50">
+        <v>51.342</v>
+      </c>
+      <c r="J45" s="50" t="s">
+        <v>374</v>
+      </c>
+      <c r="K45" s="50">
+        <v>0.475</v>
+      </c>
+      <c r="L45" s="50" t="s">
+        <v>375</v>
+      </c>
+      <c r="M45" s="50">
+        <v>0.69</v>
+      </c>
+      <c r="N45" s="50" t="s">
         <v>376</v>
       </c>
-      <c r="O26" s="41">
-        <v>0.669</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="43"/>
-      <c r="B27" s="41" t="s">
+      <c r="O45" s="50">
+        <v>0.685</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="45"/>
+      <c r="B46" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="C46" s="45"/>
+      <c r="D46" s="42">
+        <v>2034.0</v>
+      </c>
+      <c r="E46" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>872</v>
+      </c>
+      <c r="G46" s="49">
+        <v>38.042</v>
+      </c>
+      <c r="H46" s="49" t="s">
+        <v>873</v>
+      </c>
+      <c r="I46" s="49">
+        <v>51.563</v>
+      </c>
+      <c r="J46" s="49" t="s">
+        <v>874</v>
+      </c>
+      <c r="K46" s="49">
+        <v>0.469</v>
+      </c>
+      <c r="L46" s="49" t="s">
+        <v>875</v>
+      </c>
+      <c r="M46" s="49">
+        <v>0.685</v>
+      </c>
+      <c r="N46" s="49" t="s">
+        <v>876</v>
+      </c>
+      <c r="O46" s="49">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="51" t="s">
+        <v>641</v>
+      </c>
+      <c r="C48" s="51" t="s">
+        <v>642</v>
+      </c>
+      <c r="D48" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="K48" s="52" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="B49" s="54" t="s">
         <v>650</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="41">
+      <c r="C49" s="55" t="s">
+        <v>644</v>
+      </c>
+      <c r="D49" s="56">
+        <v>277.0</v>
+      </c>
+      <c r="E49" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" s="56" t="s">
+        <v>651</v>
+      </c>
+      <c r="G49" s="57">
+        <v>38.968</v>
+      </c>
+      <c r="H49" s="56" t="s">
+        <v>654</v>
+      </c>
+      <c r="I49" s="56">
+        <v>0.665</v>
+      </c>
+      <c r="J49" s="56" t="s">
+        <v>655</v>
+      </c>
+      <c r="K49" s="56">
+        <v>0.658</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="55" t="s">
+        <v>662</v>
+      </c>
+      <c r="D50" s="56">
+        <v>1049.0</v>
+      </c>
+      <c r="E50" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="56" t="s">
+        <v>668</v>
+      </c>
+      <c r="G50" s="57">
+        <v>38.051</v>
+      </c>
+      <c r="H50" s="56" t="s">
+        <v>671</v>
+      </c>
+      <c r="I50" s="56">
+        <v>0.682</v>
+      </c>
+      <c r="J50" s="56" t="s">
+        <v>672</v>
+      </c>
+      <c r="K50" s="56">
+        <v>0.677</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="55" t="s">
+        <v>678</v>
+      </c>
+      <c r="D51" s="56">
+        <v>639.0</v>
+      </c>
+      <c r="E51" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="56" t="s">
+        <v>684</v>
+      </c>
+      <c r="G51" s="57">
+        <v>40.147</v>
+      </c>
+      <c r="H51" s="56" t="s">
+        <v>687</v>
+      </c>
+      <c r="I51" s="56">
+        <v>0.647</v>
+      </c>
+      <c r="J51" s="56" t="s">
+        <v>688</v>
+      </c>
+      <c r="K51" s="56">
+        <v>0.646</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" s="55" t="s">
+        <v>694</v>
+      </c>
+      <c r="D52" s="56">
+        <v>364.0</v>
+      </c>
+      <c r="E52" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="56" t="s">
+        <v>700</v>
+      </c>
+      <c r="G52" s="57">
+        <v>39.022</v>
+      </c>
+      <c r="H52" s="56" t="s">
+        <v>703</v>
+      </c>
+      <c r="I52" s="56">
+        <v>0.666</v>
+      </c>
+      <c r="J52" s="56" t="s">
+        <v>704</v>
+      </c>
+      <c r="K52" s="56">
+        <v>0.657</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="55" t="s">
+        <v>710</v>
+      </c>
+      <c r="D53" s="56">
+        <v>1070.0</v>
+      </c>
+      <c r="E53" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="56" t="s">
+        <v>716</v>
+      </c>
+      <c r="G53" s="57">
+        <v>37.808</v>
+      </c>
+      <c r="H53" s="56" t="s">
+        <v>719</v>
+      </c>
+      <c r="I53" s="56">
+        <v>0.686</v>
+      </c>
+      <c r="J53" s="56" t="s">
+        <v>720</v>
+      </c>
+      <c r="K53" s="56">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="55" t="s">
+        <v>726</v>
+      </c>
+      <c r="D54" s="51">
+        <v>660.0</v>
+      </c>
+      <c r="E54" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="51" t="s">
+        <v>732</v>
+      </c>
+      <c r="G54" s="58">
+        <v>37.557</v>
+      </c>
+      <c r="H54" s="51" t="s">
+        <v>735</v>
+      </c>
+      <c r="I54" s="51">
+        <v>0.689</v>
+      </c>
+      <c r="J54" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="K54" s="51">
+        <v>0.685</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="55" t="s">
+        <v>742</v>
+      </c>
+      <c r="D55" s="56">
+        <v>385.0</v>
+      </c>
+      <c r="E55" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" s="56" t="s">
+        <v>748</v>
+      </c>
+      <c r="G55" s="57">
+        <v>38.593</v>
+      </c>
+      <c r="H55" s="56" t="s">
+        <v>751</v>
+      </c>
+      <c r="I55" s="56">
+        <v>0.672</v>
+      </c>
+      <c r="J55" s="56" t="s">
+        <v>752</v>
+      </c>
+      <c r="K55" s="56">
+        <v>0.664</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="55" t="s">
+        <v>758</v>
+      </c>
+      <c r="D56" s="56">
+        <v>1432.0</v>
+      </c>
+      <c r="E56" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="56" t="s">
+        <v>764</v>
+      </c>
+      <c r="G56" s="57">
+        <v>37.904</v>
+      </c>
+      <c r="H56" s="56" t="s">
+        <v>767</v>
+      </c>
+      <c r="I56" s="56">
+        <v>0.685</v>
+      </c>
+      <c r="J56" s="56" t="s">
+        <v>768</v>
+      </c>
+      <c r="K56" s="56">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="55" t="s">
+        <v>774</v>
+      </c>
+      <c r="D57" s="56">
         <v>1157.0</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E57" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="41" t="s">
-        <v>779</v>
-      </c>
-      <c r="G27" s="41">
+      <c r="F57" s="56" t="s">
+        <v>780</v>
+      </c>
+      <c r="G57" s="57">
         <v>37.978</v>
       </c>
-      <c r="H27" s="41" t="s">
-        <v>780</v>
-      </c>
-      <c r="I27" s="41">
-        <v>51.835</v>
-      </c>
-      <c r="J27" s="41" t="s">
-        <v>781</v>
-      </c>
-      <c r="K27" s="41">
-        <v>0.468</v>
-      </c>
-      <c r="L27" s="41" t="s">
-        <v>782</v>
-      </c>
-      <c r="M27" s="41">
+      <c r="H57" s="56" t="s">
+        <v>783</v>
+      </c>
+      <c r="I57" s="56">
         <v>0.684</v>
       </c>
-      <c r="N27" s="41" t="s">
-        <v>783</v>
-      </c>
-      <c r="O27" s="41">
+      <c r="J57" s="56" t="s">
+        <v>784</v>
+      </c>
+      <c r="K57" s="56">
         <v>0.679</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="43"/>
-      <c r="B28" s="41" t="s">
-        <v>656</v>
-      </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="41">
-        <v>1630.0</v>
-      </c>
-      <c r="E28" s="41" t="s">
+    <row r="58">
+      <c r="C58" s="55" t="s">
+        <v>790</v>
+      </c>
+      <c r="D58" s="56">
+        <v>747.0</v>
+      </c>
+      <c r="E58" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="41" t="s">
-        <v>784</v>
-      </c>
-      <c r="G28" s="41">
-        <v>38.252</v>
-      </c>
-      <c r="H28" s="41" t="s">
-        <v>785</v>
-      </c>
-      <c r="I28" s="41">
-        <v>51.816</v>
-      </c>
-      <c r="J28" s="41" t="s">
-        <v>786</v>
-      </c>
-      <c r="K28" s="41">
-        <v>0.461</v>
-      </c>
-      <c r="L28" s="41" t="s">
-        <v>787</v>
-      </c>
-      <c r="M28" s="41">
-        <v>0.679</v>
-      </c>
-      <c r="N28" s="41" t="s">
-        <v>788</v>
-      </c>
-      <c r="O28" s="41">
+      <c r="F58" s="56" t="s">
+        <v>796</v>
+      </c>
+      <c r="G58" s="57">
+        <v>38.423</v>
+      </c>
+      <c r="H58" s="56" t="s">
+        <v>741</v>
+      </c>
+      <c r="I58" s="56">
+        <v>0.678</v>
+      </c>
+      <c r="J58" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="K58" s="56">
         <v>0.672</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="43"/>
-      <c r="B29" s="41" t="s">
-        <v>643</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>789</v>
-      </c>
-      <c r="D29" s="41">
-        <v>964.0</v>
-      </c>
-      <c r="E29" s="41" t="s">
+    <row r="59">
+      <c r="C59" s="55" t="s">
+        <v>804</v>
+      </c>
+      <c r="D59" s="51">
+        <v>1453.0</v>
+      </c>
+      <c r="E59" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="41" t="s">
-        <v>790</v>
-      </c>
-      <c r="G29" s="41">
-        <v>38.57</v>
-      </c>
-      <c r="H29" s="41" t="s">
-        <v>791</v>
-      </c>
-      <c r="I29" s="41">
-        <v>51.989</v>
-      </c>
-      <c r="J29" s="41" t="s">
-        <v>792</v>
-      </c>
-      <c r="K29" s="41">
-        <v>0.454</v>
-      </c>
-      <c r="L29" s="41" t="s">
-        <v>793</v>
-      </c>
-      <c r="M29" s="41">
-        <v>0.674</v>
-      </c>
-      <c r="N29" s="41" t="s">
-        <v>794</v>
-      </c>
-      <c r="O29" s="41">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43"/>
-      <c r="B30" s="41" t="s">
-        <v>650</v>
-      </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="41">
-        <v>747.0</v>
-      </c>
-      <c r="E30" s="41" t="s">
+      <c r="F59" s="51" t="s">
+        <v>810</v>
+      </c>
+      <c r="G59" s="58">
+        <v>37.672</v>
+      </c>
+      <c r="H59" s="51" t="s">
+        <v>813</v>
+      </c>
+      <c r="I59" s="51">
+        <v>0.689</v>
+      </c>
+      <c r="J59" s="51" t="s">
+        <v>814</v>
+      </c>
+      <c r="K59" s="51">
+        <v>0.684</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="55" t="s">
+        <v>820</v>
+      </c>
+      <c r="D60" s="56">
+        <v>1178.0</v>
+      </c>
+      <c r="E60" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="41" t="s">
-        <v>795</v>
-      </c>
-      <c r="G30" s="41">
-        <v>38.423</v>
-      </c>
-      <c r="H30" s="41" t="s">
-        <v>796</v>
-      </c>
-      <c r="I30" s="41">
-        <v>51.579</v>
-      </c>
-      <c r="J30" s="41" t="s">
-        <v>797</v>
-      </c>
-      <c r="K30" s="41">
-        <v>0.46</v>
-      </c>
-      <c r="L30" s="41" t="s">
-        <v>741</v>
-      </c>
-      <c r="M30" s="41">
-        <v>0.678</v>
-      </c>
-      <c r="N30" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="O30" s="41">
-        <v>0.672</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="43"/>
-      <c r="B31" s="41" t="s">
-        <v>656</v>
-      </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="41">
-        <v>1220.0</v>
-      </c>
-      <c r="E31" s="41" t="s">
+      <c r="F60" s="56" t="s">
+        <v>826</v>
+      </c>
+      <c r="G60" s="57">
+        <v>38.011</v>
+      </c>
+      <c r="H60" s="56" t="s">
+        <v>829</v>
+      </c>
+      <c r="I60" s="56">
+        <v>0.685</v>
+      </c>
+      <c r="J60" s="56" t="s">
+        <v>830</v>
+      </c>
+      <c r="K60" s="56">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="55" t="s">
+        <v>835</v>
+      </c>
+      <c r="D61" s="56">
+        <v>768.0</v>
+      </c>
+      <c r="E61" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="41" t="s">
-        <v>798</v>
-      </c>
-      <c r="G31" s="41">
-        <v>38.622</v>
-      </c>
-      <c r="H31" s="41" t="s">
-        <v>799</v>
-      </c>
-      <c r="I31" s="41">
-        <v>51.711</v>
-      </c>
-      <c r="J31" s="41" t="s">
-        <v>800</v>
-      </c>
-      <c r="K31" s="41">
-        <v>0.46</v>
-      </c>
-      <c r="L31" s="41" t="s">
-        <v>801</v>
-      </c>
-      <c r="M31" s="41">
-        <v>0.678</v>
-      </c>
-      <c r="N31" s="41" t="s">
-        <v>802</v>
-      </c>
-      <c r="O31" s="41">
-        <v>0.672</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43"/>
-      <c r="B32" s="41" t="s">
-        <v>643</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>803</v>
-      </c>
-      <c r="D32" s="41">
-        <v>1670.0</v>
-      </c>
-      <c r="E32" s="41" t="s">
+      <c r="F61" s="56" t="s">
+        <v>841</v>
+      </c>
+      <c r="G61" s="57">
+        <v>37.655</v>
+      </c>
+      <c r="H61" s="56" t="s">
+        <v>844</v>
+      </c>
+      <c r="I61" s="56">
+        <v>0.688</v>
+      </c>
+      <c r="J61" s="56" t="s">
+        <v>845</v>
+      </c>
+      <c r="K61" s="56">
+        <v>0.682</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="55" t="s">
+        <v>850</v>
+      </c>
+      <c r="D62" s="56">
+        <v>1540.0</v>
+      </c>
+      <c r="E62" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="47" t="s">
-        <v>804</v>
-      </c>
-      <c r="G32" s="41">
-        <v>38.271</v>
-      </c>
-      <c r="H32" s="47" t="s">
-        <v>805</v>
-      </c>
-      <c r="I32" s="41">
-        <v>51.62</v>
-      </c>
-      <c r="J32" s="47" t="s">
-        <v>806</v>
-      </c>
-      <c r="K32" s="41">
-        <v>0.466</v>
-      </c>
-      <c r="L32" s="47" t="s">
-        <v>807</v>
-      </c>
-      <c r="M32" s="41">
+      <c r="F62" s="56" t="s">
+        <v>856</v>
+      </c>
+      <c r="G62" s="57">
+        <v>37.897</v>
+      </c>
+      <c r="H62" s="56" t="s">
+        <v>859</v>
+      </c>
+      <c r="I62" s="56">
+        <v>0.687</v>
+      </c>
+      <c r="J62" s="56" t="s">
+        <v>860</v>
+      </c>
+      <c r="K62" s="56">
         <v>0.683</v>
       </c>
-      <c r="N32" s="47" t="s">
-        <v>808</v>
-      </c>
-      <c r="O32" s="41">
-        <v>0.678</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="43"/>
-      <c r="B33" s="38" t="s">
-        <v>650</v>
-      </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="38">
-        <v>1453.0</v>
-      </c>
-      <c r="E33" s="38" t="s">
+    </row>
+    <row r="63">
+      <c r="C63" s="55" t="s">
+        <v>866</v>
+      </c>
+      <c r="D63" s="56">
+        <v>1561.0</v>
+      </c>
+      <c r="E63" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="38" t="s">
-        <v>809</v>
-      </c>
-      <c r="G33" s="38">
-        <v>37.672</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>810</v>
-      </c>
-      <c r="I33" s="38">
-        <v>51.357</v>
-      </c>
-      <c r="J33" s="38" t="s">
-        <v>811</v>
-      </c>
-      <c r="K33" s="38">
-        <v>0.475</v>
-      </c>
-      <c r="L33" s="38" t="s">
-        <v>812</v>
-      </c>
-      <c r="M33" s="38">
-        <v>0.689</v>
-      </c>
-      <c r="N33" s="38" t="s">
-        <v>813</v>
-      </c>
-      <c r="O33" s="38">
-        <v>0.684</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="43"/>
-      <c r="B34" s="41" t="s">
-        <v>656</v>
-      </c>
-      <c r="C34" s="44"/>
-      <c r="D34" s="41">
-        <v>1926.0</v>
-      </c>
-      <c r="E34" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="41" t="s">
-        <v>814</v>
-      </c>
-      <c r="G34" s="41">
-        <v>38.077</v>
-      </c>
-      <c r="H34" s="41" t="s">
-        <v>815</v>
-      </c>
-      <c r="I34" s="41">
-        <v>51.831</v>
-      </c>
-      <c r="J34" s="41" t="s">
-        <v>816</v>
-      </c>
-      <c r="K34" s="41">
-        <v>0.464</v>
-      </c>
-      <c r="L34" s="41" t="s">
-        <v>817</v>
-      </c>
-      <c r="M34" s="41">
-        <v>0.681</v>
-      </c>
-      <c r="N34" s="41" t="s">
-        <v>818</v>
-      </c>
-      <c r="O34" s="41">
-        <v>0.676</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="43"/>
-      <c r="B35" s="41" t="s">
-        <v>643</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>819</v>
-      </c>
-      <c r="D35" s="41">
-        <v>1395.0</v>
-      </c>
-      <c r="E35" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="41" t="s">
-        <v>820</v>
-      </c>
-      <c r="G35" s="41">
-        <v>38.022</v>
-      </c>
-      <c r="H35" s="41" t="s">
-        <v>821</v>
-      </c>
-      <c r="I35" s="41">
-        <v>51.66</v>
-      </c>
-      <c r="J35" s="41" t="s">
-        <v>822</v>
-      </c>
-      <c r="K35" s="41">
-        <v>0.467</v>
-      </c>
-      <c r="L35" s="41" t="s">
-        <v>823</v>
-      </c>
-      <c r="M35" s="41">
-        <v>0.683</v>
-      </c>
-      <c r="N35" s="41" t="s">
-        <v>824</v>
-      </c>
-      <c r="O35" s="41">
-        <v>0.677</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="43"/>
-      <c r="B36" s="41" t="s">
-        <v>650</v>
-      </c>
-      <c r="C36" s="43"/>
-      <c r="D36" s="41">
-        <v>1178.0</v>
-      </c>
-      <c r="E36" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="41" t="s">
-        <v>825</v>
-      </c>
-      <c r="G36" s="41">
-        <v>38.011</v>
-      </c>
-      <c r="H36" s="41" t="s">
-        <v>826</v>
-      </c>
-      <c r="I36" s="41">
-        <v>51.852</v>
-      </c>
-      <c r="J36" s="41" t="s">
-        <v>827</v>
-      </c>
-      <c r="K36" s="41">
-        <v>0.469</v>
-      </c>
-      <c r="L36" s="41" t="s">
-        <v>828</v>
-      </c>
-      <c r="M36" s="41">
-        <v>0.685</v>
-      </c>
-      <c r="N36" s="41" t="s">
-        <v>829</v>
-      </c>
-      <c r="O36" s="41">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="43"/>
-      <c r="B37" s="41" t="s">
-        <v>656</v>
-      </c>
-      <c r="C37" s="44"/>
-      <c r="D37" s="41">
-        <v>1651.0</v>
-      </c>
-      <c r="E37" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F37" s="41" t="s">
-        <v>830</v>
-      </c>
-      <c r="G37" s="41">
-        <v>38.128</v>
-      </c>
-      <c r="H37" s="41" t="s">
-        <v>831</v>
-      </c>
-      <c r="I37" s="41">
-        <v>51.767</v>
-      </c>
-      <c r="J37" s="41" t="s">
-        <v>832</v>
-      </c>
-      <c r="K37" s="41">
-        <v>0.463</v>
-      </c>
-      <c r="L37" s="41" t="s">
-        <v>833</v>
-      </c>
-      <c r="M37" s="41">
-        <v>0.681</v>
-      </c>
-      <c r="N37" s="41" t="s">
-        <v>725</v>
-      </c>
-      <c r="O37" s="41">
-        <v>0.676</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="43"/>
-      <c r="B38" s="41" t="s">
-        <v>643</v>
-      </c>
-      <c r="C38" s="42" t="s">
-        <v>834</v>
-      </c>
-      <c r="D38" s="41">
-        <v>985.0</v>
-      </c>
-      <c r="E38" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>835</v>
-      </c>
-      <c r="G38" s="41">
-        <v>37.901</v>
-      </c>
-      <c r="H38" s="41" t="s">
-        <v>836</v>
-      </c>
-      <c r="I38" s="41">
-        <v>51.013</v>
-      </c>
-      <c r="J38" s="41" t="s">
-        <v>837</v>
-      </c>
-      <c r="K38" s="41">
-        <v>0.472</v>
-      </c>
-      <c r="L38" s="41" t="s">
-        <v>838</v>
-      </c>
-      <c r="M38" s="41">
-        <v>0.687</v>
-      </c>
-      <c r="N38" s="41" t="s">
-        <v>839</v>
-      </c>
-      <c r="O38" s="41">
-        <v>0.681</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="43"/>
-      <c r="B39" s="41" t="s">
-        <v>650</v>
-      </c>
-      <c r="C39" s="43"/>
-      <c r="D39" s="41">
-        <v>768.0</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>840</v>
-      </c>
-      <c r="G39" s="41">
-        <v>37.655</v>
-      </c>
-      <c r="H39" s="41" t="s">
-        <v>841</v>
-      </c>
-      <c r="I39" s="41">
-        <v>50.954</v>
-      </c>
-      <c r="J39" s="41" t="s">
-        <v>842</v>
-      </c>
-      <c r="K39" s="41">
-        <v>0.473</v>
-      </c>
-      <c r="L39" s="41" t="s">
-        <v>843</v>
-      </c>
-      <c r="M39" s="41">
-        <v>0.688</v>
-      </c>
-      <c r="N39" s="41" t="s">
-        <v>844</v>
-      </c>
-      <c r="O39" s="41">
-        <v>0.682</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="43"/>
-      <c r="B40" s="41" t="s">
-        <v>656</v>
-      </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="41">
-        <v>1241.0</v>
-      </c>
-      <c r="E40" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>845</v>
-      </c>
-      <c r="G40" s="41">
-        <v>37.913</v>
-      </c>
-      <c r="H40" s="41" t="s">
-        <v>846</v>
-      </c>
-      <c r="I40" s="41">
-        <v>51.288</v>
-      </c>
-      <c r="J40" s="41" t="s">
-        <v>847</v>
-      </c>
-      <c r="K40" s="41">
-        <v>0.466</v>
-      </c>
-      <c r="L40" s="41" t="s">
-        <v>389</v>
-      </c>
-      <c r="M40" s="41">
-        <v>0.682</v>
-      </c>
-      <c r="N40" s="41" t="s">
-        <v>848</v>
-      </c>
-      <c r="O40" s="41">
-        <v>0.676</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="43"/>
-      <c r="B41" s="41" t="s">
-        <v>643</v>
-      </c>
-      <c r="C41" s="42" t="s">
-        <v>849</v>
-      </c>
-      <c r="D41" s="41">
-        <v>1757.0</v>
-      </c>
-      <c r="E41" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F41" s="41" t="s">
-        <v>850</v>
-      </c>
-      <c r="G41" s="41">
-        <v>37.78</v>
-      </c>
-      <c r="H41" s="41" t="s">
-        <v>851</v>
-      </c>
-      <c r="I41" s="41">
-        <v>51.35</v>
-      </c>
-      <c r="J41" s="41" t="s">
-        <v>852</v>
-      </c>
-      <c r="K41" s="41">
-        <v>0.471</v>
-      </c>
-      <c r="L41" s="41" t="s">
-        <v>853</v>
-      </c>
-      <c r="M41" s="41">
-        <v>0.686</v>
-      </c>
-      <c r="N41" s="41" t="s">
-        <v>854</v>
-      </c>
-      <c r="O41" s="41">
-        <v>0.681</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="43"/>
-      <c r="B42" s="41" t="s">
-        <v>650</v>
-      </c>
-      <c r="C42" s="43"/>
-      <c r="D42" s="41">
-        <v>1540.0</v>
-      </c>
-      <c r="E42" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="41" t="s">
-        <v>855</v>
-      </c>
-      <c r="G42" s="41">
-        <v>37.897</v>
-      </c>
-      <c r="H42" s="41" t="s">
-        <v>856</v>
-      </c>
-      <c r="I42" s="41">
-        <v>51.491</v>
-      </c>
-      <c r="J42" s="41" t="s">
-        <v>857</v>
-      </c>
-      <c r="K42" s="41">
-        <v>0.472</v>
-      </c>
-      <c r="L42" s="41" t="s">
-        <v>858</v>
-      </c>
-      <c r="M42" s="41">
-        <v>0.687</v>
-      </c>
-      <c r="N42" s="41" t="s">
-        <v>859</v>
-      </c>
-      <c r="O42" s="41">
-        <v>0.683</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="43"/>
-      <c r="B43" s="41" t="s">
-        <v>656</v>
-      </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="41">
-        <v>2013.0</v>
-      </c>
-      <c r="E43" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F43" s="41" t="s">
-        <v>860</v>
-      </c>
-      <c r="G43" s="41">
-        <v>37.936</v>
-      </c>
-      <c r="H43" s="41" t="s">
-        <v>861</v>
-      </c>
-      <c r="I43" s="41">
-        <v>51.388</v>
-      </c>
-      <c r="J43" s="41" t="s">
-        <v>862</v>
-      </c>
-      <c r="K43" s="41">
-        <v>0.472</v>
-      </c>
-      <c r="L43" s="41" t="s">
-        <v>863</v>
-      </c>
-      <c r="M43" s="41">
-        <v>0.687</v>
-      </c>
-      <c r="N43" s="41" t="s">
-        <v>864</v>
-      </c>
-      <c r="O43" s="41">
-        <v>0.683</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="43"/>
-      <c r="B44" s="41" t="s">
-        <v>643</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>865</v>
-      </c>
-      <c r="D44" s="41">
-        <v>1778.0</v>
-      </c>
-      <c r="E44" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F44" s="48" t="s">
-        <v>866</v>
-      </c>
-      <c r="G44" s="48">
-        <v>38.118</v>
-      </c>
-      <c r="H44" s="48" t="s">
-        <v>867</v>
-      </c>
-      <c r="I44" s="48">
-        <v>51.612</v>
-      </c>
-      <c r="J44" s="48" t="s">
-        <v>868</v>
-      </c>
-      <c r="K44" s="48">
-        <v>0.466</v>
-      </c>
-      <c r="L44" s="48" t="s">
-        <v>869</v>
-      </c>
-      <c r="M44" s="48">
-        <v>0.683</v>
-      </c>
-      <c r="N44" s="48" t="s">
-        <v>870</v>
-      </c>
-      <c r="O44" s="48">
-        <v>0.676</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="43"/>
-      <c r="B45" s="38" t="s">
-        <v>650</v>
-      </c>
-      <c r="C45" s="43"/>
-      <c r="D45" s="41">
-        <v>1561.0</v>
-      </c>
-      <c r="E45" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F45" s="49" t="s">
-        <v>871</v>
-      </c>
-      <c r="G45" s="49">
+      <c r="F63" s="59" t="s">
+        <v>372</v>
+      </c>
+      <c r="G63" s="60">
         <v>37.712</v>
       </c>
-      <c r="H45" s="49" t="s">
-        <v>872</v>
-      </c>
-      <c r="I45" s="49">
-        <v>51.342</v>
-      </c>
-      <c r="J45" s="49" t="s">
-        <v>873</v>
-      </c>
-      <c r="K45" s="49">
-        <v>0.475</v>
-      </c>
-      <c r="L45" s="49" t="s">
-        <v>874</v>
-      </c>
-      <c r="M45" s="49">
+      <c r="H63" s="59" t="s">
+        <v>375</v>
+      </c>
+      <c r="I63" s="59">
         <v>0.69</v>
       </c>
-      <c r="N45" s="49" t="s">
-        <v>875</v>
-      </c>
-      <c r="O45" s="49">
-        <v>0.685</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="44"/>
-      <c r="B46" s="41" t="s">
-        <v>656</v>
-      </c>
-      <c r="C46" s="44"/>
-      <c r="D46" s="41">
-        <v>2034.0</v>
-      </c>
-      <c r="E46" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="48" t="s">
-        <v>876</v>
-      </c>
-      <c r="G46" s="48">
-        <v>38.042</v>
-      </c>
-      <c r="H46" s="48" t="s">
-        <v>877</v>
-      </c>
-      <c r="I46" s="48">
-        <v>51.563</v>
-      </c>
-      <c r="J46" s="48" t="s">
-        <v>878</v>
-      </c>
-      <c r="K46" s="48">
-        <v>0.469</v>
-      </c>
-      <c r="L46" s="48" t="s">
-        <v>879</v>
-      </c>
-      <c r="M46" s="48">
-        <v>0.685</v>
-      </c>
-      <c r="N46" s="48" t="s">
-        <v>880</v>
-      </c>
-      <c r="O46" s="48">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="50" t="s">
-        <v>641</v>
-      </c>
-      <c r="C48" s="50" t="s">
-        <v>642</v>
-      </c>
-      <c r="D48" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="E48" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="51" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="H48" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="I48" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="J48" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="K48" s="51" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="52" t="s">
-        <v>348</v>
-      </c>
-      <c r="B49" s="53" t="s">
-        <v>650</v>
-      </c>
-      <c r="C49" s="54" t="s">
-        <v>644</v>
-      </c>
-      <c r="D49" s="55">
-        <v>277.0</v>
-      </c>
-      <c r="E49" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F49" s="55" t="s">
-        <v>651</v>
-      </c>
-      <c r="G49" s="56">
-        <v>38.968</v>
-      </c>
-      <c r="H49" s="55" t="s">
-        <v>654</v>
-      </c>
-      <c r="I49" s="55">
-        <v>0.665</v>
-      </c>
-      <c r="J49" s="55" t="s">
-        <v>655</v>
-      </c>
-      <c r="K49" s="55">
-        <v>0.658</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="54" t="s">
-        <v>662</v>
-      </c>
-      <c r="D50" s="55">
-        <v>1049.0</v>
-      </c>
-      <c r="E50" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="55" t="s">
-        <v>668</v>
-      </c>
-      <c r="G50" s="56">
-        <v>38.051</v>
-      </c>
-      <c r="H50" s="55" t="s">
-        <v>671</v>
-      </c>
-      <c r="I50" s="55">
-        <v>0.682</v>
-      </c>
-      <c r="J50" s="55" t="s">
-        <v>672</v>
-      </c>
-      <c r="K50" s="55">
-        <v>0.677</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" s="54" t="s">
-        <v>678</v>
-      </c>
-      <c r="D51" s="55">
-        <v>639.0</v>
-      </c>
-      <c r="E51" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" s="55" t="s">
-        <v>684</v>
-      </c>
-      <c r="G51" s="56">
-        <v>40.147</v>
-      </c>
-      <c r="H51" s="55" t="s">
-        <v>687</v>
-      </c>
-      <c r="I51" s="55">
-        <v>0.647</v>
-      </c>
-      <c r="J51" s="55" t="s">
-        <v>688</v>
-      </c>
-      <c r="K51" s="55">
-        <v>0.646</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" s="54" t="s">
-        <v>694</v>
-      </c>
-      <c r="D52" s="55">
-        <v>364.0</v>
-      </c>
-      <c r="E52" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F52" s="55" t="s">
-        <v>700</v>
-      </c>
-      <c r="G52" s="56">
-        <v>39.022</v>
-      </c>
-      <c r="H52" s="55" t="s">
-        <v>703</v>
-      </c>
-      <c r="I52" s="55">
-        <v>0.666</v>
-      </c>
-      <c r="J52" s="55" t="s">
-        <v>704</v>
-      </c>
-      <c r="K52" s="55">
-        <v>0.657</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" s="54" t="s">
-        <v>710</v>
-      </c>
-      <c r="D53" s="55">
-        <v>1070.0</v>
-      </c>
-      <c r="E53" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F53" s="55" t="s">
-        <v>716</v>
-      </c>
-      <c r="G53" s="56">
-        <v>37.808</v>
-      </c>
-      <c r="H53" s="55" t="s">
-        <v>719</v>
-      </c>
-      <c r="I53" s="55">
-        <v>0.686</v>
-      </c>
-      <c r="J53" s="55" t="s">
-        <v>720</v>
-      </c>
-      <c r="K53" s="55">
-        <v>0.681</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" s="54" t="s">
-        <v>726</v>
-      </c>
-      <c r="D54" s="50">
-        <v>660.0</v>
-      </c>
-      <c r="E54" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="F54" s="50" t="s">
-        <v>732</v>
-      </c>
-      <c r="G54" s="57">
-        <v>37.557</v>
-      </c>
-      <c r="H54" s="50" t="s">
-        <v>735</v>
-      </c>
-      <c r="I54" s="50">
-        <v>0.689</v>
-      </c>
-      <c r="J54" s="50" t="s">
-        <v>736</v>
-      </c>
-      <c r="K54" s="50">
-        <v>0.685</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" s="54" t="s">
-        <v>742</v>
-      </c>
-      <c r="D55" s="55">
-        <v>385.0</v>
-      </c>
-      <c r="E55" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F55" s="55" t="s">
-        <v>748</v>
-      </c>
-      <c r="G55" s="56">
-        <v>38.593</v>
-      </c>
-      <c r="H55" s="55" t="s">
-        <v>751</v>
-      </c>
-      <c r="I55" s="55">
-        <v>0.672</v>
-      </c>
-      <c r="J55" s="55" t="s">
-        <v>752</v>
-      </c>
-      <c r="K55" s="55">
-        <v>0.664</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" s="54" t="s">
-        <v>758</v>
-      </c>
-      <c r="D56" s="55">
-        <v>1432.0</v>
-      </c>
-      <c r="E56" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F56" s="55" t="s">
-        <v>764</v>
-      </c>
-      <c r="G56" s="56">
-        <v>37.904</v>
-      </c>
-      <c r="H56" s="55" t="s">
-        <v>767</v>
-      </c>
-      <c r="I56" s="55">
-        <v>0.685</v>
-      </c>
-      <c r="J56" s="55" t="s">
-        <v>768</v>
-      </c>
-      <c r="K56" s="55">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" s="54" t="s">
-        <v>774</v>
-      </c>
-      <c r="D57" s="55">
-        <v>1157.0</v>
-      </c>
-      <c r="E57" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F57" s="55" t="s">
-        <v>779</v>
-      </c>
-      <c r="G57" s="56">
-        <v>37.978</v>
-      </c>
-      <c r="H57" s="55" t="s">
-        <v>782</v>
-      </c>
-      <c r="I57" s="55">
-        <v>0.684</v>
-      </c>
-      <c r="J57" s="55" t="s">
-        <v>783</v>
-      </c>
-      <c r="K57" s="55">
-        <v>0.679</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" s="54" t="s">
-        <v>789</v>
-      </c>
-      <c r="D58" s="55">
-        <v>747.0</v>
-      </c>
-      <c r="E58" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F58" s="55" t="s">
-        <v>795</v>
-      </c>
-      <c r="G58" s="56">
-        <v>38.423</v>
-      </c>
-      <c r="H58" s="55" t="s">
-        <v>741</v>
-      </c>
-      <c r="I58" s="55">
-        <v>0.678</v>
-      </c>
-      <c r="J58" s="55" t="s">
-        <v>213</v>
-      </c>
-      <c r="K58" s="55">
-        <v>0.672</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" s="54" t="s">
-        <v>803</v>
-      </c>
-      <c r="D59" s="50">
-        <v>1453.0</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" s="50" t="s">
-        <v>809</v>
-      </c>
-      <c r="G59" s="57">
-        <v>37.672</v>
-      </c>
-      <c r="H59" s="50" t="s">
-        <v>812</v>
-      </c>
-      <c r="I59" s="50">
-        <v>0.689</v>
-      </c>
-      <c r="J59" s="50" t="s">
-        <v>813</v>
-      </c>
-      <c r="K59" s="50">
-        <v>0.684</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60" s="54" t="s">
-        <v>819</v>
-      </c>
-      <c r="D60" s="55">
-        <v>1178.0</v>
-      </c>
-      <c r="E60" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F60" s="55" t="s">
-        <v>825</v>
-      </c>
-      <c r="G60" s="56">
-        <v>38.011</v>
-      </c>
-      <c r="H60" s="55" t="s">
-        <v>828</v>
-      </c>
-      <c r="I60" s="55">
-        <v>0.685</v>
-      </c>
-      <c r="J60" s="55" t="s">
-        <v>829</v>
-      </c>
-      <c r="K60" s="55">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" s="54" t="s">
-        <v>834</v>
-      </c>
-      <c r="D61" s="55">
-        <v>768.0</v>
-      </c>
-      <c r="E61" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F61" s="55" t="s">
-        <v>840</v>
-      </c>
-      <c r="G61" s="56">
-        <v>37.655</v>
-      </c>
-      <c r="H61" s="55" t="s">
-        <v>843</v>
-      </c>
-      <c r="I61" s="55">
-        <v>0.688</v>
-      </c>
-      <c r="J61" s="55" t="s">
-        <v>844</v>
-      </c>
-      <c r="K61" s="55">
-        <v>0.682</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="C62" s="54" t="s">
-        <v>849</v>
-      </c>
-      <c r="D62" s="55">
-        <v>1540.0</v>
-      </c>
-      <c r="E62" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F62" s="55" t="s">
-        <v>855</v>
-      </c>
-      <c r="G62" s="56">
-        <v>37.897</v>
-      </c>
-      <c r="H62" s="55" t="s">
-        <v>858</v>
-      </c>
-      <c r="I62" s="55">
-        <v>0.687</v>
-      </c>
-      <c r="J62" s="55" t="s">
-        <v>859</v>
-      </c>
-      <c r="K62" s="55">
-        <v>0.683</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="C63" s="54" t="s">
-        <v>865</v>
-      </c>
-      <c r="D63" s="55">
-        <v>1561.0</v>
-      </c>
-      <c r="E63" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F63" s="58" t="s">
-        <v>871</v>
-      </c>
-      <c r="G63" s="59">
-        <v>37.712</v>
-      </c>
-      <c r="H63" s="58" t="s">
-        <v>874</v>
-      </c>
-      <c r="I63" s="58">
-        <v>0.69</v>
-      </c>
-      <c r="J63" s="58" t="s">
-        <v>875</v>
-      </c>
-      <c r="K63" s="58">
+      <c r="J63" s="59" t="s">
+        <v>376</v>
+      </c>
+      <c r="K63" s="59">
         <v>0.685</v>
       </c>
     </row>
@@ -11600,54 +11591,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="39" t="s">
         <v>641</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="39" t="s">
         <v>642</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="40" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="48" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="47" t="s">
-        <v>881</v>
-      </c>
-      <c r="D2" s="47">
+      <c r="C2" s="48" t="s">
+        <v>877</v>
+      </c>
+      <c r="D2" s="48">
         <v>1586.0</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="47">
+      <c r="F2" s="48">
         <v>0.356</v>
       </c>
-      <c r="G2" s="60">
+      <c r="G2" s="61">
         <v>0.597</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="61">
         <v>0.622</v>
       </c>
     </row>
@@ -11677,175 +11668,175 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="G1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="H1" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="62" t="s">
+      <c r="I1" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="J1" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="K1" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="62" t="s">
+      <c r="L1" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="62" t="s">
+      <c r="M1" s="63" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="s">
-        <v>882</v>
-      </c>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="64" t="s">
+        <v>878</v>
+      </c>
+      <c r="B2" s="65" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="14">
         <v>1780.0</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="E2" s="5">
         <v>42.244</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="G2" s="5">
         <v>55.599</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="I2" s="5">
         <v>0.359</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="K2" s="5">
         <v>0.599</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="M2" s="5">
         <v>0.599</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="63" t="s">
-        <v>888</v>
-      </c>
-      <c r="B3" s="64" t="s">
+      <c r="A3" s="64" t="s">
+        <v>884</v>
+      </c>
+      <c r="B3" s="65" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="14">
         <v>1780.0</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="E3" s="6">
         <v>42.783</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="G3" s="6">
         <v>56.398</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="I3" s="6">
         <v>0.346</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="K3" s="6">
         <v>0.588</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="M3" s="6">
         <v>0.588</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="65" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="14">
         <v>1780.0</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="E4" s="6">
         <v>40.74</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G4" s="6">
         <v>54.172</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>896</v>
-      </c>
-      <c r="I4" s="65">
+        <v>892</v>
+      </c>
+      <c r="I4" s="66">
         <v>0.413</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="K4" s="6">
         <v>0.643</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="M4" s="6">
         <v>0.633</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="64" t="s">
         <v>404</v>
       </c>
-      <c r="B5" s="64" t="s">
-        <v>899</v>
+      <c r="B5" s="65" t="s">
+        <v>895</v>
       </c>
       <c r="C5" s="14">
         <v>1780.0</v>
@@ -11882,11 +11873,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="64" t="s">
         <v>463</v>
       </c>
-      <c r="B6" s="64" t="s">
-        <v>899</v>
+      <c r="B6" s="65" t="s">
+        <v>895</v>
       </c>
       <c r="C6" s="14">
         <v>1780.0</v>
@@ -11923,11 +11914,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="s">
-        <v>900</v>
-      </c>
-      <c r="B7" s="64" t="s">
-        <v>899</v>
+      <c r="A7" s="64" t="s">
+        <v>896</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>895</v>
       </c>
       <c r="C7" s="14">
         <v>1780.0</v>
@@ -11964,11 +11955,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="63" t="s">
-        <v>901</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>899</v>
+      <c r="A8" s="64" t="s">
+        <v>897</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>895</v>
       </c>
       <c r="C8" s="14">
         <v>1780.0</v>
@@ -12005,934 +11996,934 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="67" t="s">
+        <v>898</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>899</v>
+      </c>
+      <c r="C9" s="68">
+        <v>1780.0</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>900</v>
+      </c>
+      <c r="E9" s="68">
+        <v>40.336</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>901</v>
+      </c>
+      <c r="G9" s="69">
+        <v>54.067</v>
+      </c>
+      <c r="H9" s="68" t="s">
         <v>902</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="I9" s="68">
+        <v>0.383</v>
+      </c>
+      <c r="J9" s="68" t="s">
         <v>903</v>
       </c>
-      <c r="C9" s="67">
+      <c r="K9" s="68">
+        <v>0.631</v>
+      </c>
+      <c r="L9" s="68" t="s">
+        <v>904</v>
+      </c>
+      <c r="M9" s="68">
+        <v>0.624</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="67" t="s">
+        <v>898</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>905</v>
+      </c>
+      <c r="C10" s="68">
         <v>1780.0</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>904</v>
-      </c>
-      <c r="E9" s="67">
-        <v>40.336</v>
-      </c>
-      <c r="F9" s="67" t="s">
-        <v>905</v>
-      </c>
-      <c r="G9" s="68">
-        <v>54.067</v>
-      </c>
-      <c r="H9" s="67" t="s">
+      <c r="D10" s="68" t="s">
         <v>906</v>
       </c>
-      <c r="I9" s="67">
-        <v>0.383</v>
-      </c>
-      <c r="J9" s="67" t="s">
+      <c r="E10" s="69">
+        <v>39.408</v>
+      </c>
+      <c r="F10" s="68" t="s">
         <v>907</v>
       </c>
-      <c r="K9" s="67">
-        <v>0.631</v>
-      </c>
-      <c r="L9" s="67" t="s">
+      <c r="G10" s="69">
+        <v>53.761</v>
+      </c>
+      <c r="H10" s="68" t="s">
         <v>908</v>
       </c>
-      <c r="M9" s="67">
-        <v>0.624</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="66" t="s">
-        <v>902</v>
-      </c>
-      <c r="B10" s="66" t="s">
+      <c r="I10" s="68">
+        <v>0.39</v>
+      </c>
+      <c r="J10" s="68" t="s">
         <v>909</v>
       </c>
-      <c r="C10" s="67">
+      <c r="K10" s="69">
+        <v>0.649</v>
+      </c>
+      <c r="L10" s="68" t="s">
+        <v>910</v>
+      </c>
+      <c r="M10" s="69">
+        <v>0.644</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="67" t="s">
+        <v>898</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>911</v>
+      </c>
+      <c r="C11" s="68">
         <v>1780.0</v>
       </c>
-      <c r="D10" s="67" t="s">
-        <v>910</v>
-      </c>
-      <c r="E10" s="68">
-        <v>39.408</v>
-      </c>
-      <c r="F10" s="67" t="s">
-        <v>911</v>
-      </c>
-      <c r="G10" s="68">
-        <v>53.761</v>
-      </c>
-      <c r="H10" s="67" t="s">
+      <c r="D11" s="68" t="s">
         <v>912</v>
       </c>
-      <c r="I10" s="67">
-        <v>0.39</v>
-      </c>
-      <c r="J10" s="67" t="s">
+      <c r="E11" s="69">
+        <v>39.31</v>
+      </c>
+      <c r="F11" s="68" t="s">
         <v>913</v>
       </c>
-      <c r="K10" s="68">
-        <v>0.649</v>
-      </c>
-      <c r="L10" s="67" t="s">
+      <c r="G11" s="69">
+        <v>53.515</v>
+      </c>
+      <c r="H11" s="68" t="s">
         <v>914</v>
       </c>
-      <c r="M10" s="68">
-        <v>0.644</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="66" t="s">
-        <v>902</v>
-      </c>
-      <c r="B11" s="66" t="s">
+      <c r="I11" s="69">
+        <v>0.395</v>
+      </c>
+      <c r="J11" s="68" t="s">
         <v>915</v>
       </c>
-      <c r="C11" s="67">
-        <v>1780.0</v>
-      </c>
-      <c r="D11" s="67" t="s">
+      <c r="K11" s="69">
+        <v>0.654</v>
+      </c>
+      <c r="L11" s="68" t="s">
         <v>916</v>
       </c>
-      <c r="E11" s="68">
-        <v>39.31</v>
-      </c>
-      <c r="F11" s="67" t="s">
-        <v>917</v>
-      </c>
-      <c r="G11" s="68">
-        <v>53.515</v>
-      </c>
-      <c r="H11" s="67" t="s">
-        <v>918</v>
-      </c>
-      <c r="I11" s="68">
-        <v>0.395</v>
-      </c>
-      <c r="J11" s="67" t="s">
-        <v>919</v>
-      </c>
-      <c r="K11" s="68">
-        <v>0.654</v>
-      </c>
-      <c r="L11" s="67" t="s">
-        <v>920</v>
-      </c>
-      <c r="M11" s="68">
+      <c r="M11" s="69">
         <v>0.648</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="D14" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="70" t="s">
+      <c r="E14" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="70" t="s">
+      <c r="F14" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="70" t="s">
+      <c r="G14" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="70" t="s">
+      <c r="H14" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="70" t="s">
+      <c r="I14" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="J14" s="70" t="s">
+      <c r="J14" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="70" t="s">
+      <c r="K14" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="70" t="s">
+      <c r="L14" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="70" t="s">
+      <c r="M14" s="71" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="72" t="s">
+        <v>878</v>
+      </c>
+      <c r="B15" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="74">
+        <v>1780.0</v>
+      </c>
+      <c r="D15" s="74" t="s">
+        <v>879</v>
+      </c>
+      <c r="E15" s="75">
+        <v>42.244</v>
+      </c>
+      <c r="F15" s="74" t="s">
+        <v>880</v>
+      </c>
+      <c r="G15" s="75">
+        <v>55.599</v>
+      </c>
+      <c r="H15" s="74" t="s">
+        <v>881</v>
+      </c>
+      <c r="I15" s="75">
+        <v>0.359</v>
+      </c>
+      <c r="J15" s="74" t="s">
         <v>882</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="K15" s="75">
+        <v>0.599</v>
+      </c>
+      <c r="L15" s="74" t="s">
+        <v>883</v>
+      </c>
+      <c r="M15" s="75">
+        <v>0.599</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="72" t="s">
+        <v>884</v>
+      </c>
+      <c r="B16" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="73">
+      <c r="C16" s="74">
         <v>1780.0</v>
       </c>
-      <c r="D15" s="73" t="s">
-        <v>883</v>
-      </c>
-      <c r="E15" s="74">
-        <v>42.244</v>
-      </c>
-      <c r="F15" s="73" t="s">
-        <v>884</v>
-      </c>
-      <c r="G15" s="74">
-        <v>55.599</v>
-      </c>
-      <c r="H15" s="73" t="s">
+      <c r="D16" s="74" t="s">
         <v>885</v>
       </c>
-      <c r="I15" s="74">
-        <v>0.359</v>
-      </c>
-      <c r="J15" s="73" t="s">
+      <c r="E16" s="75">
+        <v>42.783</v>
+      </c>
+      <c r="F16" s="75" t="s">
         <v>886</v>
       </c>
-      <c r="K15" s="74">
-        <v>0.599</v>
-      </c>
-      <c r="L15" s="73" t="s">
+      <c r="G16" s="75">
+        <v>56.398</v>
+      </c>
+      <c r="H16" s="75" t="s">
         <v>887</v>
       </c>
-      <c r="M15" s="74">
-        <v>0.599</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="71" t="s">
+      <c r="I16" s="75">
+        <v>0.346</v>
+      </c>
+      <c r="J16" s="75" t="s">
         <v>888</v>
       </c>
-      <c r="B16" s="72" t="s">
+      <c r="K16" s="75">
+        <v>0.588</v>
+      </c>
+      <c r="L16" s="75" t="s">
+        <v>889</v>
+      </c>
+      <c r="M16" s="75">
+        <v>0.588</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="73">
+      <c r="C17" s="74">
         <v>1780.0</v>
       </c>
-      <c r="D16" s="73" t="s">
-        <v>889</v>
-      </c>
-      <c r="E16" s="74">
-        <v>42.783</v>
-      </c>
-      <c r="F16" s="74" t="s">
+      <c r="D17" s="74" t="s">
         <v>890</v>
       </c>
-      <c r="G16" s="74">
-        <v>56.398</v>
-      </c>
-      <c r="H16" s="74" t="s">
+      <c r="E17" s="75">
+        <v>40.74</v>
+      </c>
+      <c r="F17" s="75" t="s">
         <v>891</v>
       </c>
-      <c r="I16" s="74">
-        <v>0.346</v>
-      </c>
-      <c r="J16" s="74" t="s">
+      <c r="G17" s="75">
+        <v>54.172</v>
+      </c>
+      <c r="H17" s="75" t="s">
         <v>892</v>
       </c>
-      <c r="K16" s="74">
-        <v>0.588</v>
-      </c>
-      <c r="L16" s="74" t="s">
+      <c r="I17" s="75">
+        <v>0.413</v>
+      </c>
+      <c r="J17" s="75" t="s">
         <v>893</v>
       </c>
-      <c r="M16" s="74">
-        <v>0.588</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="71" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="72" t="s">
+      <c r="K17" s="75">
+        <v>0.643</v>
+      </c>
+      <c r="L17" s="75" t="s">
+        <v>894</v>
+      </c>
+      <c r="M17" s="75">
+        <v>0.633</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="73">
+      <c r="C18" s="74">
         <v>1780.0</v>
       </c>
-      <c r="D17" s="73" t="s">
-        <v>894</v>
-      </c>
-      <c r="E17" s="74">
-        <v>40.74</v>
-      </c>
-      <c r="F17" s="74" t="s">
-        <v>895</v>
-      </c>
-      <c r="G17" s="74">
-        <v>54.172</v>
-      </c>
-      <c r="H17" s="74" t="s">
-        <v>896</v>
-      </c>
-      <c r="I17" s="74">
-        <v>0.413</v>
-      </c>
-      <c r="J17" s="74" t="s">
-        <v>897</v>
-      </c>
-      <c r="K17" s="74">
-        <v>0.643</v>
-      </c>
-      <c r="L17" s="74" t="s">
-        <v>898</v>
-      </c>
-      <c r="M17" s="74">
-        <v>0.633</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="75" t="s">
-        <v>168</v>
-      </c>
-      <c r="B18" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="73">
-        <v>1780.0</v>
-      </c>
       <c r="D18" s="14" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E18" s="14">
         <v>39.539</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="G18" s="30">
         <v>53.183</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="I18" s="30">
         <v>0.418</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="K18" s="14">
         <v>0.65</v>
       </c>
       <c r="L18" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="M18" s="78">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="72" t="s">
+        <v>404</v>
+      </c>
+      <c r="B19" s="73" t="s">
+        <v>895</v>
+      </c>
+      <c r="C19" s="74">
+        <v>1780.0</v>
+      </c>
+      <c r="D19" s="74" t="s">
+        <v>415</v>
+      </c>
+      <c r="E19" s="74">
+        <v>40.175</v>
+      </c>
+      <c r="F19" s="74" t="s">
+        <v>416</v>
+      </c>
+      <c r="G19" s="74">
+        <v>54.336</v>
+      </c>
+      <c r="H19" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="I19" s="74">
+        <v>0.409</v>
+      </c>
+      <c r="J19" s="74" t="s">
+        <v>418</v>
+      </c>
+      <c r="K19" s="74">
+        <v>0.639</v>
+      </c>
+      <c r="L19" s="74" t="s">
+        <v>419</v>
+      </c>
+      <c r="M19" s="74">
+        <v>0.636</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="72" t="s">
+        <v>463</v>
+      </c>
+      <c r="B20" s="73" t="s">
+        <v>895</v>
+      </c>
+      <c r="C20" s="74">
+        <v>1780.0</v>
+      </c>
+      <c r="D20" s="74" t="s">
+        <v>473</v>
+      </c>
+      <c r="E20" s="74">
+        <v>40.859</v>
+      </c>
+      <c r="F20" s="74" t="s">
+        <v>474</v>
+      </c>
+      <c r="G20" s="74">
+        <v>54.846</v>
+      </c>
+      <c r="H20" s="74" t="s">
+        <v>475</v>
+      </c>
+      <c r="I20" s="74">
+        <v>0.39</v>
+      </c>
+      <c r="J20" s="74" t="s">
+        <v>476</v>
+      </c>
+      <c r="K20" s="74">
+        <v>0.624</v>
+      </c>
+      <c r="L20" s="74" t="s">
+        <v>477</v>
+      </c>
+      <c r="M20" s="74">
+        <v>0.617</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="72" t="s">
+        <v>896</v>
+      </c>
+      <c r="B21" s="73" t="s">
+        <v>895</v>
+      </c>
+      <c r="C21" s="74">
+        <v>1780.0</v>
+      </c>
+      <c r="D21" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="E21" s="74">
+        <v>40.528</v>
+      </c>
+      <c r="F21" s="74" t="s">
+        <v>593</v>
+      </c>
+      <c r="G21" s="74">
+        <v>55.083</v>
+      </c>
+      <c r="H21" s="74" t="s">
+        <v>594</v>
+      </c>
+      <c r="I21" s="74">
+        <v>0.393</v>
+      </c>
+      <c r="J21" s="74" t="s">
+        <v>595</v>
+      </c>
+      <c r="K21" s="74">
+        <v>0.627</v>
+      </c>
+      <c r="L21" s="74" t="s">
+        <v>596</v>
+      </c>
+      <c r="M21" s="74">
+        <v>0.633</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="72" t="s">
+        <v>897</v>
+      </c>
+      <c r="B22" s="72" t="s">
+        <v>895</v>
+      </c>
+      <c r="C22" s="74">
+        <v>1780.0</v>
+      </c>
+      <c r="D22" s="74" t="s">
+        <v>531</v>
+      </c>
+      <c r="E22" s="74">
+        <v>41.114</v>
+      </c>
+      <c r="F22" s="74" t="s">
+        <v>532</v>
+      </c>
+      <c r="G22" s="74">
+        <v>55.313</v>
+      </c>
+      <c r="H22" s="74" t="s">
+        <v>533</v>
+      </c>
+      <c r="I22" s="74">
+        <v>0.373</v>
+      </c>
+      <c r="J22" s="74" t="s">
+        <v>534</v>
+      </c>
+      <c r="K22" s="74">
+        <v>0.611</v>
+      </c>
+      <c r="L22" s="74" t="s">
+        <v>535</v>
+      </c>
+      <c r="M22" s="74">
+        <v>0.603</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B23" s="79" t="s">
+        <v>899</v>
+      </c>
+      <c r="C23" s="80">
+        <v>1780.0</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>900</v>
+      </c>
+      <c r="E23" s="69">
+        <v>39.523</v>
+      </c>
+      <c r="F23" s="68" t="s">
+        <v>901</v>
+      </c>
+      <c r="G23" s="69">
+        <v>53.708</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>902</v>
+      </c>
+      <c r="I23" s="68">
+        <v>0.391</v>
+      </c>
+      <c r="J23" s="68" t="s">
+        <v>903</v>
+      </c>
+      <c r="K23" s="69">
+        <v>0.65</v>
+      </c>
+      <c r="L23" s="68" t="s">
+        <v>904</v>
+      </c>
+      <c r="M23" s="69">
+        <v>0.644</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>905</v>
+      </c>
+      <c r="C24" s="80">
+        <v>1780.0</v>
+      </c>
+      <c r="D24" s="68" t="s">
+        <v>923</v>
+      </c>
+      <c r="E24" s="69">
+        <v>39.672</v>
+      </c>
+      <c r="F24" s="68" t="s">
+        <v>924</v>
+      </c>
+      <c r="G24" s="69">
+        <v>53.428</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>925</v>
+      </c>
+      <c r="I24" s="68">
+        <v>0.397</v>
+      </c>
+      <c r="J24" s="68" t="s">
         <v>926</v>
       </c>
-      <c r="M18" s="77">
-        <v>0.647</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="71" t="s">
-        <v>404</v>
-      </c>
-      <c r="B19" s="72" t="s">
-        <v>899</v>
-      </c>
-      <c r="C19" s="73">
+      <c r="K24" s="69">
+        <v>0.65</v>
+      </c>
+      <c r="L24" s="68" t="s">
+        <v>927</v>
+      </c>
+      <c r="M24" s="69">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B25" s="79" t="s">
+        <v>911</v>
+      </c>
+      <c r="C25" s="80">
         <v>1780.0</v>
       </c>
-      <c r="D19" s="73" t="s">
-        <v>415</v>
-      </c>
-      <c r="E19" s="73">
-        <v>40.175</v>
-      </c>
-      <c r="F19" s="73" t="s">
-        <v>416</v>
-      </c>
-      <c r="G19" s="73">
-        <v>54.336</v>
-      </c>
-      <c r="H19" s="73" t="s">
-        <v>417</v>
-      </c>
-      <c r="I19" s="73">
-        <v>0.409</v>
-      </c>
-      <c r="J19" s="73" t="s">
-        <v>418</v>
-      </c>
-      <c r="K19" s="73">
-        <v>0.639</v>
-      </c>
-      <c r="L19" s="73" t="s">
-        <v>419</v>
-      </c>
-      <c r="M19" s="73">
-        <v>0.636</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="71" t="s">
-        <v>463</v>
-      </c>
-      <c r="B20" s="72" t="s">
-        <v>899</v>
-      </c>
-      <c r="C20" s="73">
-        <v>1780.0</v>
-      </c>
-      <c r="D20" s="73" t="s">
-        <v>473</v>
-      </c>
-      <c r="E20" s="73">
-        <v>40.859</v>
-      </c>
-      <c r="F20" s="73" t="s">
-        <v>474</v>
-      </c>
-      <c r="G20" s="73">
-        <v>54.846</v>
-      </c>
-      <c r="H20" s="73" t="s">
-        <v>475</v>
-      </c>
-      <c r="I20" s="73">
-        <v>0.39</v>
-      </c>
-      <c r="J20" s="73" t="s">
-        <v>476</v>
-      </c>
-      <c r="K20" s="73">
-        <v>0.624</v>
-      </c>
-      <c r="L20" s="73" t="s">
-        <v>477</v>
-      </c>
-      <c r="M20" s="73">
-        <v>0.617</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="71" t="s">
-        <v>900</v>
-      </c>
-      <c r="B21" s="72" t="s">
-        <v>899</v>
-      </c>
-      <c r="C21" s="73">
-        <v>1780.0</v>
-      </c>
-      <c r="D21" s="73" t="s">
-        <v>592</v>
-      </c>
-      <c r="E21" s="73">
-        <v>40.528</v>
-      </c>
-      <c r="F21" s="73" t="s">
-        <v>593</v>
-      </c>
-      <c r="G21" s="73">
-        <v>55.083</v>
-      </c>
-      <c r="H21" s="73" t="s">
-        <v>594</v>
-      </c>
-      <c r="I21" s="73">
-        <v>0.393</v>
-      </c>
-      <c r="J21" s="73" t="s">
-        <v>595</v>
-      </c>
-      <c r="K21" s="73">
-        <v>0.627</v>
-      </c>
-      <c r="L21" s="73" t="s">
-        <v>596</v>
-      </c>
-      <c r="M21" s="73">
+      <c r="D25" s="68" t="s">
+        <v>928</v>
+      </c>
+      <c r="E25" s="69">
+        <v>39.17</v>
+      </c>
+      <c r="F25" s="68" t="s">
+        <v>929</v>
+      </c>
+      <c r="G25" s="69">
+        <v>53.193</v>
+      </c>
+      <c r="H25" s="68" t="s">
+        <v>930</v>
+      </c>
+      <c r="I25" s="68">
+        <v>0.403</v>
+      </c>
+      <c r="J25" s="68" t="s">
+        <v>931</v>
+      </c>
+      <c r="K25" s="69">
+        <v>0.657</v>
+      </c>
+      <c r="L25" s="68" t="s">
+        <v>932</v>
+      </c>
+      <c r="M25" s="69">
+        <v>0.653</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="71" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="72" t="s">
+        <v>878</v>
+      </c>
+      <c r="B29" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="74" t="s">
+        <v>879</v>
+      </c>
+      <c r="D29" s="75">
+        <v>42.244</v>
+      </c>
+      <c r="E29" s="74" t="s">
+        <v>882</v>
+      </c>
+      <c r="F29" s="75">
+        <v>0.599</v>
+      </c>
+      <c r="G29" s="74" t="s">
+        <v>883</v>
+      </c>
+      <c r="H29" s="75">
+        <v>0.599</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="72" t="s">
+        <v>884</v>
+      </c>
+      <c r="B30" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="74" t="s">
+        <v>885</v>
+      </c>
+      <c r="D30" s="75">
+        <v>42.783</v>
+      </c>
+      <c r="E30" s="75" t="s">
+        <v>888</v>
+      </c>
+      <c r="F30" s="75">
+        <v>0.588</v>
+      </c>
+      <c r="G30" s="75" t="s">
+        <v>889</v>
+      </c>
+      <c r="H30" s="75">
+        <v>0.588</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="74" t="s">
+        <v>890</v>
+      </c>
+      <c r="D31" s="75">
+        <v>40.74</v>
+      </c>
+      <c r="E31" s="75" t="s">
+        <v>893</v>
+      </c>
+      <c r="F31" s="75">
+        <v>0.643</v>
+      </c>
+      <c r="G31" s="75" t="s">
+        <v>894</v>
+      </c>
+      <c r="H31" s="75">
         <v>0.633</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="71" t="s">
-        <v>901</v>
-      </c>
-      <c r="B22" s="71" t="s">
-        <v>899</v>
-      </c>
-      <c r="C22" s="73">
-        <v>1780.0</v>
-      </c>
-      <c r="D22" s="73" t="s">
-        <v>531</v>
-      </c>
-      <c r="E22" s="73">
-        <v>41.114</v>
-      </c>
-      <c r="F22" s="73" t="s">
-        <v>532</v>
-      </c>
-      <c r="G22" s="73">
-        <v>55.313</v>
-      </c>
-      <c r="H22" s="73" t="s">
-        <v>533</v>
-      </c>
-      <c r="I22" s="73">
-        <v>0.373</v>
-      </c>
-      <c r="J22" s="73" t="s">
-        <v>534</v>
-      </c>
-      <c r="K22" s="73">
-        <v>0.611</v>
-      </c>
-      <c r="L22" s="73" t="s">
-        <v>535</v>
-      </c>
-      <c r="M22" s="73">
-        <v>0.603</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="78" t="s">
-        <v>902</v>
-      </c>
-      <c r="B23" s="78" t="s">
-        <v>903</v>
-      </c>
-      <c r="C23" s="79">
-        <v>1780.0</v>
-      </c>
-      <c r="D23" s="67" t="s">
-        <v>904</v>
-      </c>
-      <c r="E23" s="68">
-        <v>39.523</v>
-      </c>
-      <c r="F23" s="67" t="s">
-        <v>905</v>
-      </c>
-      <c r="G23" s="68">
-        <v>53.708</v>
-      </c>
-      <c r="H23" s="67" t="s">
-        <v>906</v>
-      </c>
-      <c r="I23" s="67">
-        <v>0.391</v>
-      </c>
-      <c r="J23" s="67" t="s">
-        <v>907</v>
-      </c>
-      <c r="K23" s="68">
-        <v>0.65</v>
-      </c>
-      <c r="L23" s="67" t="s">
-        <v>908</v>
-      </c>
-      <c r="M23" s="68">
-        <v>0.644</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="78" t="s">
-        <v>902</v>
-      </c>
-      <c r="B24" s="78" t="s">
-        <v>909</v>
-      </c>
-      <c r="C24" s="79">
-        <v>1780.0</v>
-      </c>
-      <c r="D24" s="67" t="s">
-        <v>927</v>
-      </c>
-      <c r="E24" s="68">
-        <v>39.672</v>
-      </c>
-      <c r="F24" s="67" t="s">
-        <v>928</v>
-      </c>
-      <c r="G24" s="68">
-        <v>53.428</v>
-      </c>
-      <c r="H24" s="67" t="s">
-        <v>929</v>
-      </c>
-      <c r="I24" s="67">
-        <v>0.397</v>
-      </c>
-      <c r="J24" s="67" t="s">
-        <v>930</v>
-      </c>
-      <c r="K24" s="68">
-        <v>0.65</v>
-      </c>
-      <c r="L24" s="67" t="s">
-        <v>931</v>
-      </c>
-      <c r="M24" s="68">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="78" t="s">
-        <v>902</v>
-      </c>
-      <c r="B25" s="78" t="s">
-        <v>915</v>
-      </c>
-      <c r="C25" s="79">
-        <v>1780.0</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>932</v>
-      </c>
-      <c r="E25" s="68">
-        <v>39.17</v>
-      </c>
-      <c r="F25" s="67" t="s">
-        <v>933</v>
-      </c>
-      <c r="G25" s="68">
-        <v>53.193</v>
-      </c>
-      <c r="H25" s="67" t="s">
-        <v>934</v>
-      </c>
-      <c r="I25" s="67">
-        <v>0.403</v>
-      </c>
-      <c r="J25" s="67" t="s">
-        <v>935</v>
-      </c>
-      <c r="K25" s="68">
-        <v>0.657</v>
-      </c>
-      <c r="L25" s="67" t="s">
-        <v>936</v>
-      </c>
-      <c r="M25" s="68">
-        <v>0.653</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="70" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="71" t="s">
-        <v>882</v>
-      </c>
-      <c r="B29" s="72" t="s">
+    <row r="32">
+      <c r="A32" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="73" t="s">
-        <v>883</v>
-      </c>
-      <c r="D29" s="74">
-        <v>42.244</v>
-      </c>
-      <c r="E29" s="73" t="s">
-        <v>886</v>
-      </c>
-      <c r="F29" s="74">
-        <v>0.599</v>
-      </c>
-      <c r="G29" s="73" t="s">
-        <v>887</v>
-      </c>
-      <c r="H29" s="74">
-        <v>0.599</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="71" t="s">
-        <v>888</v>
-      </c>
-      <c r="B30" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="73" t="s">
-        <v>889</v>
-      </c>
-      <c r="D30" s="74">
-        <v>42.783</v>
-      </c>
-      <c r="E30" s="74" t="s">
-        <v>892</v>
-      </c>
-      <c r="F30" s="74">
-        <v>0.588</v>
-      </c>
-      <c r="G30" s="74" t="s">
-        <v>893</v>
-      </c>
-      <c r="H30" s="74">
-        <v>0.588</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="71" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="73" t="s">
-        <v>894</v>
-      </c>
-      <c r="D31" s="74">
-        <v>40.74</v>
-      </c>
-      <c r="E31" s="74" t="s">
-        <v>897</v>
-      </c>
-      <c r="F31" s="74">
-        <v>0.643</v>
-      </c>
-      <c r="G31" s="74" t="s">
-        <v>898</v>
-      </c>
-      <c r="H31" s="74">
-        <v>0.633</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="75" t="s">
-        <v>168</v>
-      </c>
-      <c r="B32" s="76" t="s">
-        <v>15</v>
-      </c>
       <c r="C32" s="14" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="D32" s="14">
         <v>39.539</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="F32" s="14">
         <v>0.65</v>
       </c>
       <c r="G32" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="H32" s="78">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="72" t="s">
+        <v>404</v>
+      </c>
+      <c r="B33" s="73" t="s">
+        <v>895</v>
+      </c>
+      <c r="C33" s="74" t="s">
+        <v>415</v>
+      </c>
+      <c r="D33" s="74">
+        <v>40.175</v>
+      </c>
+      <c r="E33" s="74" t="s">
+        <v>418</v>
+      </c>
+      <c r="F33" s="74">
+        <v>0.639</v>
+      </c>
+      <c r="G33" s="74" t="s">
+        <v>419</v>
+      </c>
+      <c r="H33" s="74">
+        <v>0.636</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="72" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34" s="73" t="s">
+        <v>895</v>
+      </c>
+      <c r="C34" s="74" t="s">
+        <v>473</v>
+      </c>
+      <c r="D34" s="74">
+        <v>40.859</v>
+      </c>
+      <c r="E34" s="74" t="s">
+        <v>476</v>
+      </c>
+      <c r="F34" s="74">
+        <v>0.624</v>
+      </c>
+      <c r="G34" s="74" t="s">
+        <v>477</v>
+      </c>
+      <c r="H34" s="74">
+        <v>0.617</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="72" t="s">
+        <v>896</v>
+      </c>
+      <c r="B35" s="73" t="s">
+        <v>895</v>
+      </c>
+      <c r="C35" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="D35" s="74">
+        <v>40.528</v>
+      </c>
+      <c r="E35" s="74" t="s">
+        <v>595</v>
+      </c>
+      <c r="F35" s="74">
+        <v>0.627</v>
+      </c>
+      <c r="G35" s="74" t="s">
+        <v>596</v>
+      </c>
+      <c r="H35" s="74">
+        <v>0.633</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="72" t="s">
+        <v>897</v>
+      </c>
+      <c r="B36" s="72" t="s">
+        <v>895</v>
+      </c>
+      <c r="C36" s="74" t="s">
+        <v>531</v>
+      </c>
+      <c r="D36" s="74">
+        <v>41.114</v>
+      </c>
+      <c r="E36" s="74" t="s">
+        <v>534</v>
+      </c>
+      <c r="F36" s="74">
+        <v>0.611</v>
+      </c>
+      <c r="G36" s="74" t="s">
+        <v>535</v>
+      </c>
+      <c r="H36" s="74">
+        <v>0.603</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B37" s="79" t="s">
+        <v>899</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>900</v>
+      </c>
+      <c r="D37" s="69">
+        <v>39.523</v>
+      </c>
+      <c r="E37" s="68" t="s">
+        <v>903</v>
+      </c>
+      <c r="F37" s="69">
+        <v>0.65</v>
+      </c>
+      <c r="G37" s="68" t="s">
+        <v>904</v>
+      </c>
+      <c r="H37" s="69">
+        <v>0.644</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B38" s="79" t="s">
+        <v>905</v>
+      </c>
+      <c r="C38" s="68" t="s">
+        <v>923</v>
+      </c>
+      <c r="D38" s="69">
+        <v>39.672</v>
+      </c>
+      <c r="E38" s="68" t="s">
         <v>926</v>
       </c>
-      <c r="H32" s="77">
-        <v>0.647</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="71" t="s">
-        <v>404</v>
-      </c>
-      <c r="B33" s="72" t="s">
-        <v>899</v>
-      </c>
-      <c r="C33" s="73" t="s">
-        <v>415</v>
-      </c>
-      <c r="D33" s="73">
-        <v>40.175</v>
-      </c>
-      <c r="E33" s="73" t="s">
-        <v>418</v>
-      </c>
-      <c r="F33" s="73">
-        <v>0.639</v>
-      </c>
-      <c r="G33" s="73" t="s">
-        <v>419</v>
-      </c>
-      <c r="H33" s="73">
-        <v>0.636</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="71" t="s">
-        <v>463</v>
-      </c>
-      <c r="B34" s="72" t="s">
-        <v>899</v>
-      </c>
-      <c r="C34" s="73" t="s">
-        <v>473</v>
-      </c>
-      <c r="D34" s="73">
-        <v>40.859</v>
-      </c>
-      <c r="E34" s="73" t="s">
-        <v>476</v>
-      </c>
-      <c r="F34" s="73">
-        <v>0.624</v>
-      </c>
-      <c r="G34" s="73" t="s">
-        <v>477</v>
-      </c>
-      <c r="H34" s="73">
-        <v>0.617</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="71" t="s">
-        <v>900</v>
-      </c>
-      <c r="B35" s="72" t="s">
-        <v>899</v>
-      </c>
-      <c r="C35" s="73" t="s">
-        <v>592</v>
-      </c>
-      <c r="D35" s="73">
-        <v>40.528</v>
-      </c>
-      <c r="E35" s="73" t="s">
-        <v>595</v>
-      </c>
-      <c r="F35" s="73">
-        <v>0.627</v>
-      </c>
-      <c r="G35" s="73" t="s">
-        <v>596</v>
-      </c>
-      <c r="H35" s="73">
-        <v>0.633</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="71" t="s">
-        <v>901</v>
-      </c>
-      <c r="B36" s="71" t="s">
-        <v>899</v>
-      </c>
-      <c r="C36" s="73" t="s">
-        <v>531</v>
-      </c>
-      <c r="D36" s="73">
-        <v>41.114</v>
-      </c>
-      <c r="E36" s="73" t="s">
-        <v>534</v>
-      </c>
-      <c r="F36" s="73">
-        <v>0.611</v>
-      </c>
-      <c r="G36" s="73" t="s">
-        <v>535</v>
-      </c>
-      <c r="H36" s="73">
-        <v>0.603</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="78" t="s">
-        <v>902</v>
-      </c>
-      <c r="B37" s="78" t="s">
-        <v>903</v>
-      </c>
-      <c r="C37" s="67" t="s">
-        <v>904</v>
-      </c>
-      <c r="D37" s="68">
-        <v>39.523</v>
-      </c>
-      <c r="E37" s="67" t="s">
-        <v>907</v>
-      </c>
-      <c r="F37" s="68">
+      <c r="F38" s="69">
         <v>0.65</v>
       </c>
-      <c r="G37" s="67" t="s">
-        <v>908</v>
-      </c>
-      <c r="H37" s="68">
-        <v>0.644</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="78" t="s">
-        <v>902</v>
-      </c>
-      <c r="B38" s="78" t="s">
-        <v>909</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="G38" s="68" t="s">
         <v>927</v>
       </c>
-      <c r="D38" s="68">
-        <v>39.672</v>
-      </c>
-      <c r="E38" s="67" t="s">
-        <v>930</v>
-      </c>
-      <c r="F38" s="68">
+      <c r="H38" s="69">
         <v>0.65</v>
       </c>
-      <c r="G38" s="67" t="s">
+    </row>
+    <row r="39">
+      <c r="A39" s="79" t="s">
+        <v>898</v>
+      </c>
+      <c r="B39" s="79" t="s">
+        <v>911</v>
+      </c>
+      <c r="C39" s="68" t="s">
+        <v>928</v>
+      </c>
+      <c r="D39" s="69">
+        <v>39.17</v>
+      </c>
+      <c r="E39" s="68" t="s">
         <v>931</v>
       </c>
-      <c r="H38" s="68">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="78" t="s">
-        <v>902</v>
-      </c>
-      <c r="B39" s="78" t="s">
-        <v>915</v>
-      </c>
-      <c r="C39" s="67" t="s">
+      <c r="F39" s="69">
+        <v>0.657</v>
+      </c>
+      <c r="G39" s="68" t="s">
         <v>932</v>
       </c>
-      <c r="D39" s="68">
-        <v>39.17</v>
-      </c>
-      <c r="E39" s="67" t="s">
-        <v>935</v>
-      </c>
-      <c r="F39" s="68">
-        <v>0.657</v>
-      </c>
-      <c r="G39" s="67" t="s">
-        <v>936</v>
-      </c>
-      <c r="H39" s="68">
+      <c r="H39" s="69">
         <v>0.653</v>
       </c>
     </row>
